--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R350b270fa5c7482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="R01a9e01bf81a4a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="R43bd138ba01544f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="R5adc94f7e5f641a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R31fbe5eaa03d420d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R1d9e576993594475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="Rf754ef26bb854b67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R15ea6c19298d4116"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="Rf052ac26fd174615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="R68851a7ad0ed4c4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="Rc53b5e9e16a948e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R2a8728b04c8941c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="Ra19c23cb39194204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R15269ccb83d64c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="Rf7f3cc8f043f4703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="Rc8fee97626764a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="Rf2e3e75a0c634ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R935130d447244229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R2df14219586d4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="R8458add22ded498b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R3c78bb7167c048e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="Ra3ade35578a544f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="Rdac7eca09df840fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="R498f01e7881146ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R56151b1de4834424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R0b054db49a2d4677"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -303,7 +303,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-19 현재 소스 92dc503f43c1+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-19 현재 소스 3874d4c74c7e에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -41142,8 +41142,8 @@
           <x:t xml:space="preserve">기본 관측시간 s</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8">
-        <x:v>600</x:v>
+      <x:c r="B8" t="n">
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>지휘흐름 화면 실제 파서 기본값</x:v>
@@ -41253,7 +41253,7 @@
         <x:v>기준 소스 버전</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>92dc503f43c1+dirty</x:v>
+        <x:v>3874d4c74c7e</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
         <x:v>Git HEAD + 미커밋 소스 여부. 아래 SHA-256은 실제 내보낸 작업 파일 내용</x:v>
@@ -41506,10 +41506,10 @@
         <x:v>화면 설정 dur</x:v>
       </x:c>
       <x:c r="B39" t="n">
-        <x:v>600</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="C39" s="3" t="str">
-        <x:v>관측 시간(초). 적용 타입=number, 선언 기본값=600. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>관측 시간(초 · 기본 1800). 적용 타입=number, 선언 기본값=1800. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -42053,7 +42053,7 @@
         <x:v>SHA-256 prototype/command-flow.html</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
-        <x:v>7970e526b3ba9418418376ebe90373ba0c54542b6a4d8f8ebf074be413b3e936</x:v>
+        <x:v>d0df1c6c5292969e097f1894c60f56227d1b6972d73994bf8aa1f9a1f6138d49</x:v>
       </x:c>
       <x:c r="C89" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R15269ccb83d64c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="Rf7f3cc8f043f4703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="Rc8fee97626764a61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="Rf2e3e75a0c634ba5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R935130d447244229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R2df14219586d4ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="R8458add22ded498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R3c78bb7167c048e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="Ra3ade35578a544f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="Rdac7eca09df840fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="R498f01e7881146ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R56151b1de4834424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R0b054db49a2d4677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Ra67af9825407451a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="R8a08be5a6ee44e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="R4c734b34c151467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="Rdace4c5026f54e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R067b3ed84a5e455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R88e60bb490c44c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="Racc7cb3b163747a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R94d4b1cee25e454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="R528a3fcce4da484d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="R33a8faecda7a41e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="R099e9588d0bf4236"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R63a7257a6a8f4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R97b6b670208f4bcc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -303,7 +303,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-19 현재 소스 3874d4c74c7e에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-28 현재 소스 93597359b07d+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -41220,7 +41220,7 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="4" t="n">
-        <x:v>46284</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="C13" s="3" t="str">
         <x:v>Asia/Seoul 기준. node scripts/export-params-xlsx.mjs</x:v>
@@ -41253,7 +41253,7 @@
         <x:v>기준 소스 버전</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>3874d4c74c7e</x:v>
+        <x:v>93597359b07d+dirty</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
         <x:v>Git HEAD + 미커밋 소스 여부. 아래 SHA-256은 실제 내보낸 작업 파일 내용</x:v>
@@ -41286,7 +41286,7 @@
         <x:v>기본 배치</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
-        <x:v>HANBANDO_LEGACY_NORMAL</x:v>
+        <x:v>HANBANDO_FULL_NORMAL</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
         <x:v>LEGACY·FULL 두 자산 시트는 동일한 화면 features를 각각 적용</x:v>
@@ -41473,10 +41473,10 @@
         <x:v>화면 설정 dep</x:v>
       </x:c>
       <x:c r="B36" s="3" t="str">
-        <x:v>HANBANDO_LEGACY_NORMAL</x:v>
+        <x:v>HANBANDO_FULL_NORMAL</x:v>
       </x:c>
       <x:c r="C36" s="3" t="str">
-        <x:v>배치 (HANBANDO_LEGACY_NORMAL|HANBANDO_FULL_NORMAL|…_MCRC_DOWN|…_KAMDOC_DOWN). 적용 타입=string, 선언 기본값="HANBANDO_LEGACY_NORMAL". 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>배치 (HANBANDO_FULL_NORMAL(기본)|HANBANDO_LEGACY_NORMAL|…_MCRC_DOWN|…_KAMDOC_DOWN). 적용 타입=string, 선언 기본값="HANBANDO_FULL_NORMAL". 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -42053,7 +42053,7 @@
         <x:v>SHA-256 prototype/command-flow.html</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
-        <x:v>d0df1c6c5292969e097f1894c60f56227d1b6972d73994bf8aa1f9a1f6138d49</x:v>
+        <x:v>6705830ef17b38d2702291527f56ceeb3d36b78b34bf179c9586990780028f48</x:v>
       </x:c>
       <x:c r="C89" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Ra67af9825407451a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="R8a08be5a6ee44e6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="R4c734b34c151467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="Rdace4c5026f54e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R067b3ed84a5e455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R88e60bb490c44c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="Racc7cb3b163747a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R94d4b1cee25e454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="R528a3fcce4da484d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="R33a8faecda7a41e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="R099e9588d0bf4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R63a7257a6a8f4738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R97b6b670208f4bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R7acb9210e8d94742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="Rf2ad7a80b13446fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="R3919f84b77e548e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="R4a3953569085471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R17ab7dace30d4191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R8d8dc722db9047dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="R4a44a83917b449b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R053fd86612dc47ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="Rc12e7dcc41ee4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="Rca6a293e86594ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="Rb4f21866dcce4ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R83ad1c7c2ba148d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R407b60786bd944d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -72,6 +72,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -303,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-28 현재 소스 93597359b07d+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-28 현재 소스 04b4f36882df+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -41253,7 +41261,7 @@
         <x:v>기준 소스 버전</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>93597359b07d+dirty</x:v>
+        <x:v>04b4f36882df+dirty</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
         <x:v>Git HEAD + 미커밋 소스 여부. 아래 SHA-256은 실제 내보낸 작업 파일 내용</x:v>
@@ -41599,139 +41607,139 @@
     </x:row>
     <x:row r="48" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A48" s="2" t="str">
-        <x:v>화면 설정 lx</x:v>
+        <x:v>화면 설정 bsrc</x:v>
       </x:c>
       <x:c r="B48" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C48" s="3" t="str">
-        <x:v>탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>탄도 위협 시작 보고원을 조기경보 레이더(그린파인)로 고정 — MCRC 경유 탄도 항적 0건 (ADR-103 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A49" s="2" t="str">
+        <x:v>화면 설정 lx</x:v>
+      </x:c>
+      <x:c r="B49" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C49" s="3" t="str">
+        <x:v>탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A50" s="2" t="str">
         <x:v>화면 설정 floor</x:v>
       </x:c>
-      <x:c r="B49" s="5" t="b">
+      <x:c r="B50" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C49" s="3" t="str">
+      <x:c r="C50" s="3" t="str">
         <x:v>C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A50" s="2" t="str">
+    <x:row r="51" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A51" s="2" t="str">
         <x:v>화면 설정 pipe</x:v>
       </x:c>
-      <x:c r="B50" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C50" s="3" t="str">
+      <x:c r="B51" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C51" s="3" t="str">
         <x:v>협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A51" s="2" t="str">
-        <x:v>화면 설정 icc</x:v>
-      </x:c>
-      <x:c r="B51" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C51" s="3" t="str">
-        <x:v>ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A52" s="2" t="str">
-        <x:v>화면 설정 iccsec</x:v>
-      </x:c>
-      <x:c r="B52" t="n">
-        <x:v>-1</x:v>
+        <x:v>화면 설정 icc</x:v>
+      </x:c>
+      <x:c r="B52" s="5" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C52" s="3" t="str">
-        <x:v>ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A53" s="2" t="str">
+        <x:v>화면 설정 iccsec</x:v>
+      </x:c>
+      <x:c r="B53" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C53" s="3" t="str">
+        <x:v>ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A54" s="2" t="str">
         <x:v>화면 설정 ecs</x:v>
       </x:c>
-      <x:c r="B53" s="5" t="b">
+      <x:c r="B54" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C53" s="3" t="str">
+      <x:c r="C54" s="3" t="str">
         <x:v>ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A54" s="2" t="str">
+    <x:row r="55" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A55" s="2" t="str">
         <x:v>화면 설정 ecssec</x:v>
       </x:c>
-      <x:c r="B54" t="n">
+      <x:c r="B55" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C54" s="3" t="str">
+      <x:c r="C55" s="3" t="str">
         <x:v>ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A55" s="2" t="str">
+    <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A56" s="2" t="str">
         <x:v>화면 설정 aim</x:v>
       </x:c>
-      <x:c r="B55" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C55" s="3" t="str">
+      <x:c r="B56" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C56" s="3" t="str">
         <x:v>표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A56" s="2" t="str">
+    <x:row r="57" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A57" s="2" t="str">
         <x:v>화면 설정 par</x:v>
       </x:c>
-      <x:c r="B56" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C56" s="3" t="str">
+      <x:c r="B57" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C57" s="3" t="str">
         <x:v>C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A57" s="2" t="str">
-        <x:v>화면 설정 issue</x:v>
-      </x:c>
-      <x:c r="B57" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C57" s="3" t="str">
-        <x:v>교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="str">
-        <x:v>화면 설정 issuesec</x:v>
-      </x:c>
-      <x:c r="B58" t="n">
-        <x:v>-1</x:v>
+        <x:v>화면 설정 issue</x:v>
+      </x:c>
+      <x:c r="B58" s="5" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C58" s="3" t="str">
-        <x:v>발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A59" s="3" t="str">
-        <x:v>엔진 기본 highResolutionDeployment</x:v>
-      </x:c>
-      <x:c r="B59" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>화면 설정 issuesec</x:v>
+      </x:c>
+      <x:c r="B59" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C59" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="3" t="str">
-        <x:v>엔진 기본 threatTargetDispersion</x:v>
+        <x:v>엔진 기본 highResolutionDeployment</x:v>
       </x:c>
       <x:c r="B60" s="5" t="b">
         <x:v>1</x:v>
@@ -41740,9 +41748,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A61" s="2" t="str">
-        <x:v>엔진 기본 southernAxes</x:v>
+    <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A61" s="3" t="str">
+        <x:v>엔진 기본 threatTargetDispersion</x:v>
       </x:c>
       <x:c r="B61" s="5" t="b">
         <x:v>1</x:v>
@@ -41753,7 +41761,7 @@
     </x:row>
     <x:row r="62" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A62" s="3" t="str">
-        <x:v>엔진 기본 linkSemanticsV2</x:v>
+        <x:v>엔진 기본 southernAxes</x:v>
       </x:c>
       <x:c r="B62" s="5" t="b">
         <x:v>1</x:v>
@@ -41764,7 +41772,7 @@
     </x:row>
     <x:row r="63" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A63" s="3" t="str">
-        <x:v>엔진 기본 sensorReportParity</x:v>
+        <x:v>엔진 기본 linkSemanticsV2</x:v>
       </x:c>
       <x:c r="B63" s="5" t="b">
         <x:v>1</x:v>
@@ -41773,9 +41781,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="64" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A64" s="3" t="str">
-        <x:v>엔진 기본 sawtoothFreshness</x:v>
+        <x:v>엔진 기본 sensorReportParity</x:v>
       </x:c>
       <x:c r="B64" s="5" t="b">
         <x:v>1</x:v>
@@ -41784,9 +41792,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A65" s="3" t="str">
-        <x:v>엔진 기본 approvalChain</x:v>
+        <x:v>엔진 기본 sawtoothFreshness</x:v>
       </x:c>
       <x:c r="B65" s="5" t="b">
         <x:v>1</x:v>
@@ -41795,9 +41803,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="66" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A66" s="3" t="str">
-        <x:v>엔진 기본 unifiedEngagementState</x:v>
+        <x:v>엔진 기본 approvalChain</x:v>
       </x:c>
       <x:c r="B66" s="5" t="b">
         <x:v>1</x:v>
@@ -41806,9 +41814,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A67" s="3" t="str">
-        <x:v>엔진 기본 selfDefenseFire</x:v>
+        <x:v>엔진 기본 unifiedEngagementState</x:v>
       </x:c>
       <x:c r="B67" s="5" t="b">
         <x:v>1</x:v>
@@ -41819,40 +41827,40 @@
     </x:row>
     <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A68" s="3" t="str">
-        <x:v>엔진 기본 engageOnRemote</x:v>
+        <x:v>엔진 기본 selfDefenseFire</x:v>
       </x:c>
       <x:c r="B68" s="5" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C68" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A69" s="3" t="str">
-        <x:v>엔진 기본 usfkTrackSharing</x:v>
-      </x:c>
-      <x:c r="B69" t="str">
-        <x:v>미지정</x:v>
+        <x:v>엔진 기본 engageOnRemote</x:v>
+      </x:c>
+      <x:c r="B69" s="5" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C69" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="str">
+        <x:v>엔진 기본 usfkTrackSharing</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>미지정</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="str">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A71" s="3" t="str">
         <x:v>엔진 기본 wtaSuitability</x:v>
-      </x:c>
-      <x:c r="B70" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C70" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A71" s="3" t="str">
-        <x:v>엔진 기본 uavLocalSelfEngage</x:v>
       </x:c>
       <x:c r="B71" s="5" t="b">
         <x:v>0</x:v>
@@ -41863,7 +41871,7 @@
     </x:row>
     <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="str">
-        <x:v>엔진 기본 earlyWarningReport</x:v>
+        <x:v>엔진 기본 uavLocalSelfEngage</x:v>
       </x:c>
       <x:c r="B72" s="5" t="b">
         <x:v>0</x:v>
@@ -41874,29 +41882,29 @@
     </x:row>
     <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="str">
-        <x:v>엔진 기본 ballisticLaunchAxes</x:v>
+        <x:v>엔진 기본 earlyWarningReport</x:v>
       </x:c>
       <x:c r="B73" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C73" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A74" s="3" t="str">
-        <x:v>엔진 기본 threatAimpoints</x:v>
+        <x:v>엔진 기본 ballisticReportSource</x:v>
       </x:c>
       <x:c r="B74" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C74" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A75" s="3" t="str">
-        <x:v>엔진 기본 c2DecisionTimeParity</x:v>
+        <x:v>엔진 기본 ballisticLaunchAxes</x:v>
       </x:c>
       <x:c r="B75" s="5" t="b">
         <x:v>0</x:v>
@@ -41907,18 +41915,18 @@
     </x:row>
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="str">
-        <x:v>엔진 기본 c2ServiceFloor</x:v>
+        <x:v>엔진 기본 threatAimpoints</x:v>
       </x:c>
       <x:c r="B76" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C76" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="str">
-        <x:v>엔진 기본 approvalPipelineRealism</x:v>
+        <x:v>엔진 기본 c2DecisionTimeParity</x:v>
       </x:c>
       <x:c r="B77" s="5" t="b">
         <x:v>0</x:v>
@@ -41927,89 +41935,89 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="str">
-        <x:v>엔진 기본 iccRelayAuthorization</x:v>
+        <x:v>엔진 기본 c2ServiceFloor</x:v>
       </x:c>
       <x:c r="B78" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C78" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="str">
-        <x:v>엔진 기본 ecsExecutionTime</x:v>
+        <x:v>엔진 기본 approvalPipelineRealism</x:v>
       </x:c>
       <x:c r="B79" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C79" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="str">
-        <x:v>엔진 기본 directiveIssueTime</x:v>
+        <x:v>엔진 기본 iccRelayAuthorization</x:v>
       </x:c>
       <x:c r="B80" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C80" s="3" t="str">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A81" s="3" t="str">
+        <x:v>엔진 기본 ecsExecutionTime</x:v>
+      </x:c>
+      <x:c r="B81" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C81" s="3" t="str">
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A81" s="3" t="str">
-        <x:v>SHA-256 js/config/system-types.js</x:v>
-      </x:c>
-      <x:c r="B81" s="3" t="str">
-        <x:v>bcfbff757b0ce78ba57dfb2d0c344a30bf943ac54cfc4c5790baa4b20b7740d6</x:v>
-      </x:c>
-      <x:c r="C81" s="3" t="str">
-        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="str">
-        <x:v>SHA-256 js/config/deployments.js</x:v>
-      </x:c>
-      <x:c r="B82" s="3" t="str">
-        <x:v>bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:v>
+        <x:v>엔진 기본 directiveIssueTime</x:v>
+      </x:c>
+      <x:c r="B82" s="7" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C82" s="3" t="str">
-        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="str">
-        <x:v>SHA-256 js/config/deployment-adapter.js</x:v>
+        <x:v>SHA-256 js/config/system-types.js</x:v>
       </x:c>
       <x:c r="B83" s="3" t="str">
-        <x:v>c4fc34a9015f3318abe0e2204d882ff0427d936dfe4ad278ebe4d47a88672cdf</x:v>
+        <x:v>c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:v>
       </x:c>
       <x:c r="C83" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="84" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="str">
-        <x:v>SHA-256 js/data/threats.js</x:v>
+        <x:v>SHA-256 js/config/deployments.js</x:v>
       </x:c>
       <x:c r="B84" s="3" t="str">
-        <x:v>155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:v>
+        <x:v>bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:v>
       </x:c>
       <x:c r="C84" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="str">
-        <x:v>SHA-256 js/data/axes.js</x:v>
+        <x:v>SHA-256 js/config/deployment-adapter.js</x:v>
       </x:c>
       <x:c r="B85" s="3" t="str">
-        <x:v>c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:v>
+        <x:v>c4fc34a9015f3318abe0e2204d882ff0427d936dfe4ad278ebe4d47a88672cdf</x:v>
       </x:c>
       <x:c r="C85" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
@@ -42017,32 +42025,32 @@
     </x:row>
     <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="str">
-        <x:v>SHA-256 js/data/scenarios.js</x:v>
+        <x:v>SHA-256 js/data/threats.js</x:v>
       </x:c>
       <x:c r="B86" s="3" t="str">
-        <x:v>e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:v>
+        <x:v>155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:v>
       </x:c>
       <x:c r="C86" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="str">
-        <x:v>SHA-256 js/engine/sim-engine.js</x:v>
+        <x:v>SHA-256 js/data/axes.js</x:v>
       </x:c>
       <x:c r="B87" s="3" t="str">
-        <x:v>45f61c3b18a7d3a93339461d878443adeb1889db8f098f1fac0f4121088f660c</x:v>
+        <x:v>c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:v>
       </x:c>
       <x:c r="C87" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="str">
-        <x:v>SHA-256 js/model/iads/c2-agent.js</x:v>
+        <x:v>SHA-256 js/data/scenarios.js</x:v>
       </x:c>
       <x:c r="B88" s="3" t="str">
-        <x:v>d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:v>
+        <x:v>e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:v>
       </x:c>
       <x:c r="C88" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
@@ -42050,10 +42058,10 @@
     </x:row>
     <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="str">
-        <x:v>SHA-256 prototype/command-flow.html</x:v>
+        <x:v>SHA-256 js/engine/sim-engine.js</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
-        <x:v>6705830ef17b38d2702291527f56ceeb3d36b78b34bf179c9586990780028f48</x:v>
+        <x:v>36cc0adb08ab2f6fd25ec8ba59a9658cbdb76d76affaeee7fa62ba30d65c3002</x:v>
       </x:c>
       <x:c r="C89" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
@@ -42061,12 +42069,34 @@
     </x:row>
     <x:row r="90" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="str">
+        <x:v>SHA-256 js/model/iads/c2-agent.js</x:v>
+      </x:c>
+      <x:c r="B90" s="3" t="str">
+        <x:v>d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:v>
+      </x:c>
+      <x:c r="C90" s="3" t="str">
+        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A91" s="3" t="str">
+        <x:v>SHA-256 prototype/command-flow.html</x:v>
+      </x:c>
+      <x:c r="B91" s="3" t="str">
+        <x:v>cdabf04b0ce94fd3e4ac456ce867946304214d385c7b19fc5b41d52b43c1a975</x:v>
+      </x:c>
+      <x:c r="C91" s="3" t="str">
+        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A92" s="3" t="str">
         <x:v>SHA-256 scripts/export-params-xlsx.mjs</x:v>
       </x:c>
-      <x:c r="B90" s="3" t="str">
+      <x:c r="B92" s="3" t="str">
         <x:v>65edfc580d2ac6dd0e9aa95587af182dc5749126d61f672f0533f4ff8c5220f6</x:v>
       </x:c>
-      <x:c r="C90" s="3" t="str">
+      <x:c r="C92" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R7acb9210e8d94742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="Rf2ad7a80b13446fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="R3919f84b77e548e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="R4a3953569085471a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="R17ab7dace30d4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="R8d8dc722db9047dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="R4a44a83917b449b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R053fd86612dc47ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="Rc12e7dcc41ee4e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="Rca6a293e86594ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="Rb4f21866dcce4ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R83ad1c7c2ba148d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R407b60786bd944d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R5060406264d14a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본설정" sheetId="2" r:id="Rcbed5db3bc574ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_LEGACY" sheetId="3" r:id="Rf0e0f148ec874058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아군자산_FULL" sheetId="4" r:id="R3cf4efc670e84f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_센서" sheetId="5" r:id="Rb8efc112b45a47b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_포대" sheetId="6" r:id="Rc3c4403d95b548f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산제원_C2" sheetId="7" r:id="R8900b925985a4075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위협제원" sheetId="8" r:id="R8f426df663ed4b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공격경로" sheetId="9" r:id="R8faea678641d4e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조준점" sheetId="10" r:id="R9f476c5bfb114d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="11" r:id="Rfe152cdef2234dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_LEGACY" sheetId="12" r:id="R01870771aada44f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신계선_FULL" sheetId="13" r:id="R5dd33172dd624a5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-28 현재 소스 04b4f36882df+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-28 현재 소스 050eac5334df+dirty에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -41261,7 +41261,7 @@
         <x:v>기준 소스 버전</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>04b4f36882df+dirty</x:v>
+        <x:v>050eac5334df+dirty</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
         <x:v>Git HEAD + 미커밋 소스 여부. 아래 SHA-256은 실제 내보낸 작업 파일 내용</x:v>
@@ -41618,150 +41618,150 @@
     </x:row>
     <x:row r="49" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A49" s="2" t="str">
-        <x:v>화면 설정 lx</x:v>
+        <x:v>화면 설정 cue</x:v>
       </x:c>
       <x:c r="B49" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C49" s="3" t="str">
-        <x:v>탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>사전대기 큐 + 긴급발사 — KAMDOC/IAOC 인지 시 상층 포대에 큐, 큐 받은 포대는 정식 명령 전 발사 가능 (ADR-104 · bsrc=1 전제 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A50" s="2" t="str">
-        <x:v>화면 설정 floor</x:v>
-      </x:c>
-      <x:c r="B50" s="5" t="b">
+        <x:v>화면 설정 cuegain</x:v>
+      </x:c>
+      <x:c r="B50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="3" t="str">
-        <x:v>C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="52.79999923706055" hidden="0" customHeight="1">
+        <x:v>큐 획득 이득 0~0.95 — 큐 도착 포대 MFR의 탐지→추적→사통 전이 시간을 (1−gain)배 (ADR-104 B-3 · 명시된 근사 · 기본 0). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A51" s="2" t="str">
-        <x:v>화면 설정 pipe</x:v>
+        <x:v>화면 설정 lx</x:v>
       </x:c>
       <x:c r="B51" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C51" s="3" t="str">
-        <x:v>협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A52" s="2" t="str">
-        <x:v>화면 설정 icc</x:v>
+        <x:v>화면 설정 floor</x:v>
       </x:c>
       <x:c r="B52" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C52" s="3" t="str">
-        <x:v>ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A53" s="2" t="str">
-        <x:v>화면 설정 iccsec</x:v>
-      </x:c>
-      <x:c r="B53" t="n">
-        <x:v>-1</x:v>
+        <x:v>화면 설정 pipe</x:v>
+      </x:c>
+      <x:c r="B53" s="5" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C53" s="3" t="str">
-        <x:v>ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A54" s="2" t="str">
-        <x:v>화면 설정 ecs</x:v>
+        <x:v>화면 설정 icc</x:v>
       </x:c>
       <x:c r="B54" s="5" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C54" s="3" t="str">
-        <x:v>ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A55" s="2" t="str">
-        <x:v>화면 설정 ecssec</x:v>
+        <x:v>화면 설정 iccsec</x:v>
       </x:c>
       <x:c r="B55" t="n">
         <x:v>-1</x:v>
       </x:c>
       <x:c r="C55" s="3" t="str">
-        <x:v>ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="2" t="str">
-        <x:v>화면 설정 aim</x:v>
+        <x:v>화면 설정 ecs</x:v>
       </x:c>
       <x:c r="B56" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C56" s="3" t="str">
-        <x:v>표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="52.79999923706055" hidden="0" customHeight="1">
+        <x:v>ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A57" s="2" t="str">
-        <x:v>화면 설정 par</x:v>
-      </x:c>
-      <x:c r="B57" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>화면 설정 ecssec</x:v>
+      </x:c>
+      <x:c r="B57" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C57" s="3" t="str">
-        <x:v>C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="str">
-        <x:v>화면 설정 issue</x:v>
+        <x:v>화면 설정 aim</x:v>
       </x:c>
       <x:c r="B58" s="5" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C58" s="3" t="str">
-        <x:v>교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A59" s="3" t="str">
-        <x:v>화면 설정 issuesec</x:v>
-      </x:c>
-      <x:c r="B59" t="n">
-        <x:v>-1</x:v>
+        <x:v>화면 설정 par</x:v>
+      </x:c>
+      <x:c r="B59" s="5" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C59" s="3" t="str">
-        <x:v>발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+        <x:v>C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="3" t="str">
-        <x:v>엔진 기본 highResolutionDeployment</x:v>
+        <x:v>화면 설정 issue</x:v>
       </x:c>
       <x:c r="B60" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C60" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="3" t="str">
-        <x:v>엔진 기본 threatTargetDispersion</x:v>
-      </x:c>
-      <x:c r="B61" s="5" t="b">
-        <x:v>1</x:v>
+        <x:v>화면 설정 issuesec</x:v>
+      </x:c>
+      <x:c r="B61" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C61" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="3" t="str">
-        <x:v>엔진 기본 southernAxes</x:v>
+        <x:v>엔진 기본 highResolutionDeployment</x:v>
       </x:c>
       <x:c r="B62" s="5" t="b">
         <x:v>1</x:v>
@@ -41770,9 +41770,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A63" s="3" t="str">
-        <x:v>엔진 기본 linkSemanticsV2</x:v>
+        <x:v>엔진 기본 threatTargetDispersion</x:v>
       </x:c>
       <x:c r="B63" s="5" t="b">
         <x:v>1</x:v>
@@ -41783,7 +41783,7 @@
     </x:row>
     <x:row r="64" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A64" s="3" t="str">
-        <x:v>엔진 기본 sensorReportParity</x:v>
+        <x:v>엔진 기본 southernAxes</x:v>
       </x:c>
       <x:c r="B64" s="5" t="b">
         <x:v>1</x:v>
@@ -41792,9 +41792,9 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A65" s="3" t="str">
-        <x:v>엔진 기본 sawtoothFreshness</x:v>
+        <x:v>엔진 기본 linkSemanticsV2</x:v>
       </x:c>
       <x:c r="B65" s="5" t="b">
         <x:v>1</x:v>
@@ -41805,7 +41805,7 @@
     </x:row>
     <x:row r="66" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A66" s="3" t="str">
-        <x:v>엔진 기본 approvalChain</x:v>
+        <x:v>엔진 기본 sensorReportParity</x:v>
       </x:c>
       <x:c r="B66" s="5" t="b">
         <x:v>1</x:v>
@@ -41816,7 +41816,7 @@
     </x:row>
     <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A67" s="3" t="str">
-        <x:v>엔진 기본 unifiedEngagementState</x:v>
+        <x:v>엔진 기본 sawtoothFreshness</x:v>
       </x:c>
       <x:c r="B67" s="5" t="b">
         <x:v>1</x:v>
@@ -41827,7 +41827,7 @@
     </x:row>
     <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A68" s="3" t="str">
-        <x:v>엔진 기본 selfDefenseFire</x:v>
+        <x:v>엔진 기본 approvalChain</x:v>
       </x:c>
       <x:c r="B68" s="5" t="b">
         <x:v>1</x:v>
@@ -41836,31 +41836,31 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A69" s="3" t="str">
-        <x:v>엔진 기본 engageOnRemote</x:v>
+        <x:v>엔진 기본 unifiedEngagementState</x:v>
       </x:c>
       <x:c r="B69" s="5" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C69" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="str">
-        <x:v>엔진 기본 usfkTrackSharing</x:v>
-      </x:c>
-      <x:c r="B70" t="str">
-        <x:v>미지정</x:v>
+        <x:v>엔진 기본 selfDefenseFire</x:v>
+      </x:c>
+      <x:c r="B70" s="5" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C70" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="str">
-        <x:v>엔진 기본 wtaSuitability</x:v>
+        <x:v>엔진 기본 engageOnRemote</x:v>
       </x:c>
       <x:c r="B71" s="5" t="b">
         <x:v>0</x:v>
@@ -41869,20 +41869,20 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="str">
-        <x:v>엔진 기본 uavLocalSelfEngage</x:v>
-      </x:c>
-      <x:c r="B72" s="5" t="b">
-        <x:v>0</x:v>
+        <x:v>엔진 기본 usfkTrackSharing</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>미지정</x:v>
       </x:c>
       <x:c r="C72" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="str">
-        <x:v>엔진 기본 earlyWarningReport</x:v>
+        <x:v>엔진 기본 wtaSuitability</x:v>
       </x:c>
       <x:c r="B73" s="5" t="b">
         <x:v>0</x:v>
@@ -41893,7 +41893,7 @@
     </x:row>
     <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A74" s="3" t="str">
-        <x:v>엔진 기본 ballisticReportSource</x:v>
+        <x:v>엔진 기본 uavLocalSelfEngage</x:v>
       </x:c>
       <x:c r="B74" s="5" t="b">
         <x:v>0</x:v>
@@ -41904,51 +41904,51 @@
     </x:row>
     <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A75" s="3" t="str">
-        <x:v>엔진 기본 ballisticLaunchAxes</x:v>
+        <x:v>엔진 기본 earlyWarningReport</x:v>
       </x:c>
       <x:c r="B75" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C75" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="str">
-        <x:v>엔진 기본 threatAimpoints</x:v>
+        <x:v>엔진 기본 ballisticReportSource</x:v>
       </x:c>
       <x:c r="B76" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C76" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="str">
-        <x:v>엔진 기본 c2DecisionTimeParity</x:v>
+        <x:v>엔진 기본 standbyCue</x:v>
       </x:c>
       <x:c r="B77" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C77" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="str">
-        <x:v>엔진 기본 c2ServiceFloor</x:v>
+        <x:v>엔진 기본 ballisticLaunchAxes</x:v>
       </x:c>
       <x:c r="B78" s="5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C78" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="str">
-        <x:v>엔진 기본 approvalPipelineRealism</x:v>
+        <x:v>엔진 기본 threatAimpoints</x:v>
       </x:c>
       <x:c r="B79" s="5" t="b">
         <x:v>0</x:v>
@@ -41959,7 +41959,7 @@
     </x:row>
     <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="str">
-        <x:v>엔진 기본 iccRelayAuthorization</x:v>
+        <x:v>엔진 기본 c2DecisionTimeParity</x:v>
       </x:c>
       <x:c r="B80" s="5" t="b">
         <x:v>0</x:v>
@@ -41970,7 +41970,7 @@
     </x:row>
     <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="str">
-        <x:v>엔진 기본 ecsExecutionTime</x:v>
+        <x:v>엔진 기본 c2ServiceFloor</x:v>
       </x:c>
       <x:c r="B81" s="7" t="b">
         <x:v>0</x:v>
@@ -41979,111 +41979,111 @@
         <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="str">
-        <x:v>엔진 기본 directiveIssueTime</x:v>
+        <x:v>엔진 기본 approvalPipelineRealism</x:v>
       </x:c>
       <x:c r="B82" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C82" s="3" t="str">
-        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="str">
+        <x:v>엔진 기본 iccRelayAuthorization</x:v>
+      </x:c>
+      <x:c r="B83" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C83" s="3" t="str">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A84" s="3" t="str">
+        <x:v>엔진 기본 ecsExecutionTime</x:v>
+      </x:c>
+      <x:c r="B84" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C84" s="3" t="str">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A85" s="3" t="str">
+        <x:v>엔진 기본 directiveIssueTime</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C85" s="3" t="str">
+        <x:v>features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A86" s="3" t="str">
         <x:v>SHA-256 js/config/system-types.js</x:v>
       </x:c>
-      <x:c r="B83" s="3" t="str">
+      <x:c r="B86" s="3" t="str">
         <x:v>c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:v>
-      </x:c>
-      <x:c r="C83" s="3" t="str">
-        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A84" s="3" t="str">
-        <x:v>SHA-256 js/config/deployments.js</x:v>
-      </x:c>
-      <x:c r="B84" s="3" t="str">
-        <x:v>bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:v>
-      </x:c>
-      <x:c r="C84" s="3" t="str">
-        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A85" s="3" t="str">
-        <x:v>SHA-256 js/config/deployment-adapter.js</x:v>
-      </x:c>
-      <x:c r="B85" s="3" t="str">
-        <x:v>c4fc34a9015f3318abe0e2204d882ff0427d936dfe4ad278ebe4d47a88672cdf</x:v>
-      </x:c>
-      <x:c r="C85" s="3" t="str">
-        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A86" s="3" t="str">
-        <x:v>SHA-256 js/data/threats.js</x:v>
-      </x:c>
-      <x:c r="B86" s="3" t="str">
-        <x:v>155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:v>
       </x:c>
       <x:c r="C86" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="str">
-        <x:v>SHA-256 js/data/axes.js</x:v>
+        <x:v>SHA-256 js/config/deployments.js</x:v>
       </x:c>
       <x:c r="B87" s="3" t="str">
-        <x:v>c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:v>
+        <x:v>bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:v>
       </x:c>
       <x:c r="C87" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="88" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="str">
-        <x:v>SHA-256 js/data/scenarios.js</x:v>
+        <x:v>SHA-256 js/config/deployment-adapter.js</x:v>
       </x:c>
       <x:c r="B88" s="3" t="str">
-        <x:v>e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:v>
+        <x:v>c4fc34a9015f3318abe0e2204d882ff0427d936dfe4ad278ebe4d47a88672cdf</x:v>
       </x:c>
       <x:c r="C88" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="str">
-        <x:v>SHA-256 js/engine/sim-engine.js</x:v>
+        <x:v>SHA-256 js/data/threats.js</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
-        <x:v>36cc0adb08ab2f6fd25ec8ba59a9658cbdb76d76affaeee7fa62ba30d65c3002</x:v>
+        <x:v>155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:v>
       </x:c>
       <x:c r="C89" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="str">
-        <x:v>SHA-256 js/model/iads/c2-agent.js</x:v>
+        <x:v>SHA-256 js/data/axes.js</x:v>
       </x:c>
       <x:c r="B90" s="3" t="str">
-        <x:v>d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:v>
+        <x:v>c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:v>
       </x:c>
       <x:c r="C90" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="str">
-        <x:v>SHA-256 prototype/command-flow.html</x:v>
+        <x:v>SHA-256 js/data/scenarios.js</x:v>
       </x:c>
       <x:c r="B91" s="3" t="str">
-        <x:v>cdabf04b0ce94fd3e4ac456ce867946304214d385c7b19fc5b41d52b43c1a975</x:v>
+        <x:v>e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:v>
       </x:c>
       <x:c r="C91" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
@@ -42091,12 +42091,45 @@
     </x:row>
     <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="str">
+        <x:v>SHA-256 js/engine/sim-engine.js</x:v>
+      </x:c>
+      <x:c r="B92" s="3" t="str">
+        <x:v>40b38fa59a5a0985cc967a15a427f3769182a8cb85bba2fef053786b75b6224b</x:v>
+      </x:c>
+      <x:c r="C92" s="3" t="str">
+        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A93" s="3" t="str">
+        <x:v>SHA-256 js/model/iads/c2-agent.js</x:v>
+      </x:c>
+      <x:c r="B93" s="3" t="str">
+        <x:v>d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:v>
+      </x:c>
+      <x:c r="C93" s="3" t="str">
+        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A94" s="3" t="str">
+        <x:v>SHA-256 prototype/command-flow.html</x:v>
+      </x:c>
+      <x:c r="B94" s="3" t="str">
+        <x:v>e1680009e5829300df68e924c6703dcba309036bec4e46c547d58cb8a2c6e887</x:v>
+      </x:c>
+      <x:c r="C94" s="3" t="str">
+        <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A95" s="3" t="str">
         <x:v>SHA-256 scripts/export-params-xlsx.mjs</x:v>
       </x:c>
-      <x:c r="B92" s="3" t="str">
+      <x:c r="B95" s="3" t="str">
         <x:v>65edfc580d2ac6dd0e9aa95587af182dc5749126d61f672f0533f4ff8c5220f6</x:v>
       </x:c>
-      <x:c r="C92" s="3" t="str">
+      <x:c r="C95" s="3" t="str">
         <x:v>작업 파일 내용 해시. 경로는 저장소 루트 기준</x:v>
       </x:c>
     </x:row>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-30 현재 소스 fa0f5d3fbeed에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-30 현재 소스 b61b500995b6에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42558,7 +42558,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">fa0f5d3fbeed</x:t>
+          <x:t xml:space="preserve">b61b500995b6</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43148,37 +43148,37 @@
     <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B54" s="5">
+          <x:t xml:space="preserve">화면 설정 nocm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호·천마 순항미사일 교전 제외 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B55" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">화면 설정 shpk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="52.79999923706055" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률을 WPN-SHORAD-PK-01(0.1/0.3/0.5)로 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 pipe</x:t>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="5">
@@ -43186,59 +43186,59 @@
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
+          <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="5">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C57" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B58">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 pipe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ecs</x:t>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C59" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ecssec</x:t>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
         </x:is>
       </x:c>
       <x:c r="B60">
@@ -43246,119 +43246,119 @@
       </x:c>
       <x:c r="C60" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 ecs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">화면 설정 ecssec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C62" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B61" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C61" s="3" t="inlineStr">
+      <x:c r="B63" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="62" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A62" s="3" t="inlineStr">
+    <x:row r="64" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B62" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
+      <x:c r="B64" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B63" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B64">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A65" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="5">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C65" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A67" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A68" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B67" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="5">
@@ -43373,7 +43373,7 @@
     <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A69" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="5">
@@ -43385,10 +43385,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="5">
@@ -43403,7 +43403,7 @@
     <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
+          <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="5">
@@ -43418,7 +43418,7 @@
     <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
+          <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="5">
@@ -43433,7 +43433,7 @@
     <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="5">
@@ -43445,42 +43445,40 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A74" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C74" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A75" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C75" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="5">
@@ -43492,25 +43490,27 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B77" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="5">
@@ -43525,7 +43525,7 @@
     <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="5">
@@ -43533,14 +43533,14 @@
       </x:c>
       <x:c r="C79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="5">
@@ -43548,14 +43548,14 @@
       </x:c>
       <x:c r="C80" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43570,24 +43570,22 @@
     <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B82" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="5">
@@ -43602,7 +43600,7 @@
     <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43614,10 +43612,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43632,25 +43630,27 @@
     <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B86" s="7">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B87" s="7">
+          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B87" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C87" s="3" t="inlineStr">
@@ -43659,13 +43659,13 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="88" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B88" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C88" s="3" t="inlineStr">
@@ -43674,25 +43674,25 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B89" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="7">
@@ -43707,97 +43707,89 @@
     <x:row r="91" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B91" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B92" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B92" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B93" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0d98a9a13251362a1408e525b7b643a6a1328ba80f4c09e5920d2c0b18a15a57</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B93" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B94" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B94" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C94" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A95" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B95" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C95" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="96" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="3" t="inlineStr">
@@ -43809,66 +43801,134 @@
     <x:row r="97" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0d98a9a13251362a1408e525b7b643a6a1328ba80f4c09e5920d2c0b18a15a57</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C97" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A99" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B99" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C99" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A101" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B97" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">65b84d17b5e7f562d3c06ef8915b71a6f9cec55f77a0124885f55b6ccf3fe7e1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C97" s="3" t="inlineStr">
+      <x:c r="B101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">f31727fbef3bfe129f113c93216b7d65e207eaafc3aeb9de7ea4f1b21106cef2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C101" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A98" s="3" t="inlineStr">
+    <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A102" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B98" s="3" t="inlineStr">
+      <x:c r="B102" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
-      <x:c r="C98" s="3" t="inlineStr">
+      <x:c r="C102" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="99" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A99" s="3" t="inlineStr">
+    <x:row r="103" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A103" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
         </x:is>
       </x:c>
-      <x:c r="B99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bf21e5188dcfb56d7d13e52b7882fe22354b7a5542e6a8fedb6dd43682c12ec3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C99" s="3" t="inlineStr">
+      <x:c r="B103" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">7e7857571866f075d0b64f3146714e8718925b9b6c981d70c392809119d73d83</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C103" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A100" s="3" t="inlineStr">
+    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A104" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B100" s="3" t="inlineStr">
+      <x:c r="B104" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">65edfc580d2ac6dd0e9aa95587af182dc5749126d61f672f0533f4ff8c5220f6</x:t>
         </x:is>
       </x:c>
-      <x:c r="C100" s="3" t="inlineStr">
+      <x:c r="C104" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-30 현재 소스 b61b500995b6에서 재내보냈습니다. 엑셀 불러오기 기능은 없습니다.</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-09-30 현재 소스 6d8763a154ff에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42558,7 +42558,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">b61b500995b6</x:t>
+          <x:t xml:space="preserve">6d8763a154ff</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43156,7 +43156,7 @@
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호·천마 순항미사일 교전 제외 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호 순항미사일 교전 제외(양 모드) · 천마는 킬웹에서만 허용 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -43171,7 +43171,7 @@
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률을 WPN-SHORAD-PK-01(0.1/0.3/0.5)로 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률 0.7 고정 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -43806,7 +43806,7 @@
       </x:c>
       <x:c r="B97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0d98a9a13251362a1408e525b7b643a6a1328ba80f4c09e5920d2c0b18a15a57</x:t>
+          <x:t xml:space="preserve">9efb329af4fe162c540a7311015d91afe502cb3c0ddbf77427e1af1ad156ba45</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="3" t="inlineStr">
@@ -43874,7 +43874,7 @@
       </x:c>
       <x:c r="B101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">f31727fbef3bfe129f113c93216b7d65e207eaafc3aeb9de7ea4f1b21106cef2</x:t>
+          <x:t xml:space="preserve">e57c173982d4789edd183662e38f1c140456839712b0d86f31db93cdb7ca140a</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="3" t="inlineStr">
@@ -43908,7 +43908,7 @@
       </x:c>
       <x:c r="B103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">7e7857571866f075d0b64f3146714e8718925b9b6c981d70c392809119d73d83</x:t>
+          <x:t xml:space="preserve">72677ddb685db2bc50861dbb367a568873100d26abc2d09042714a800a8418cd</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
@@ -43925,7 +43925,7 @@
       </x:c>
       <x:c r="B104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">65edfc580d2ac6dd0e9aa95587af182dc5749126d61f672f0533f4ff8c5220f6</x:t>
+          <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="3" t="inlineStr">

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-09-30 현재 소스 6d8763a154ff에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 9f742779cd3e에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42518,7 +42518,7 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="4">
-        <x:v>46295</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="C13" s="3" t="inlineStr">
         <x:is>
@@ -42558,7 +42558,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">6d8763a154ff</x:t>
+          <x:t xml:space="preserve">9f742779cd3e</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43178,202 +43178,202 @@
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B56" s="5">
+          <x:t xml:space="preserve">화면 설정 ea</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">조기 사수 지정 — 예상 요격 창 기준으로 항적 접수 시점에 사수를 정하고 「준비되면 쏘라」 명령 (ADR-109 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C57" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A58" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
-      <x:c r="B57" s="5">
+      <x:c r="B58" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C57" s="3" t="inlineStr">
+      <x:c r="C58" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="58" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A58" s="2" t="inlineStr">
+    <x:row r="59" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A59" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 pipe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B58" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C58" s="3" t="inlineStr">
+      <x:c r="B59" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C59" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A59" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B59" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B60">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C60" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A62" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 ecs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B61" s="5">
+      <x:c r="B62" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C61" s="3" t="inlineStr">
+      <x:c r="C62" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="62" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A62" s="2" t="inlineStr">
+    <x:row r="63" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A63" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 ecssec</x:t>
         </x:is>
       </x:c>
-      <x:c r="B62">
+      <x:c r="B63">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
+      <x:c r="C63" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A63" s="2" t="inlineStr">
+    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A64" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
+      <x:c r="B64" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="64" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A64" s="3" t="inlineStr">
+    <x:row r="65" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A65" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B64" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
+      <x:c r="B65" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C65" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B65" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C66" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A67" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B67" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C67" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A68" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C68" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A69" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="5">
@@ -43388,7 +43388,7 @@
     <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="5">
@@ -43403,67 +43403,67 @@
     <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C71" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A72" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B71" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C71" s="3" t="inlineStr">
+      <x:c r="B72" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C72" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A72" s="3" t="inlineStr">
+    <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A73" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B72" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C72" s="3" t="inlineStr">
+      <x:c r="B73" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A73" s="3" t="inlineStr">
+    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A74" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B73" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
+      <x:c r="B74" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A74" s="3" t="inlineStr">
+    <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A75" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B74" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="5">
@@ -43478,54 +43478,54 @@
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C76" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B78" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C78" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A79" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B78" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="5">
@@ -43540,7 +43540,7 @@
     <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="5">
@@ -43555,7 +43555,7 @@
     <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43563,14 +43563,14 @@
       </x:c>
       <x:c r="C81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="5">
@@ -43585,7 +43585,7 @@
     <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="5">
@@ -43600,7 +43600,7 @@
     <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43615,7 +43615,7 @@
     <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43630,24 +43630,22 @@
     <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B86" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B86" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43662,22 +43660,24 @@
     <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B88" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="5">
@@ -43692,25 +43692,25 @@
     <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B90" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B90" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B91" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C91" s="3" t="inlineStr">
@@ -43719,10 +43719,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="92" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="7">
@@ -43730,14 +43730,14 @@
       </x:c>
       <x:c r="C92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="7">
@@ -43745,14 +43745,14 @@
       </x:c>
       <x:c r="C93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="7">
@@ -43760,87 +43760,83 @@
       </x:c>
       <x:c r="C94" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A95" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B95" s="7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C95" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B96" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B96" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C97" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A99" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B97" s="3" t="inlineStr">
+      <x:c r="B99" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9efb329af4fe162c540a7311015d91afe502cb3c0ddbf77427e1af1ad156ba45</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C97" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="3" t="inlineStr">
@@ -43852,46 +43848,46 @@
     <x:row r="100" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A100" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A102" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B100" s="3" t="inlineStr">
+      <x:c r="B102" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">e57c173982d4789edd183662e38f1c140456839712b0d86f31db93cdb7ca140a</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="3" t="inlineStr">
@@ -43903,12 +43899,12 @@
     <x:row r="103" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">72677ddb685db2bc50861dbb367a568873100d26abc2d09042714a800a8418cd</x:t>
+          <x:t xml:space="preserve">6973de42ffd4e594469ebc152bea8be25f65fc6381d86e963a97fc028ac52ff2</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
@@ -43920,15 +43916,49 @@
     <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A104" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A105" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B105" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">9023d821b4d8d38094983a9b3962900835a2ac0f7bacc0c019dff8d3a8d1041a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C105" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A106" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B104" s="3" t="inlineStr">
+      <x:c r="B106" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
-      <x:c r="C104" s="3" t="inlineStr">
+      <x:c r="C106" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 9f742779cd3e에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 166352715a5a에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42558,7 +42558,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">9f742779cd3e</x:t>
+          <x:t xml:space="preserve">166352715a5a</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -42941,52 +42941,52 @@
     <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 sw</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">위협 생성 구간(초 · 0이면 관측 시간과 같음). 관측 시간보다 짧게 주면 그 뒤로 새 위협이 생기지 않아 관측 종료 시 미해결(관측 절단)을 없앨 수 있음(예: ?sw=1800&amp;dur=3600). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A41" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 x</x:t>
         </x:is>
       </x:c>
-      <x:c r="B40">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C40" s="3" t="inlineStr">
+      <x:c r="B41">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C41" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">위협 생성 강도 — 시나리오 도착률 배수 (0.1~10 · 기본 1 · 고급 모의설정에서도 조절). 적용 타입=number, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="41" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A41" s="2" t="inlineStr">
+    <x:row r="42" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A42" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 appr</x:t>
         </x:is>
       </x:c>
-      <x:c r="B41" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C41" s="3" t="inlineStr">
+      <x:c r="B42" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">교전 협조 계선 — 국지방공 AOC↔MCRC 협조 (ADR-058·065·098). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A42" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 cop</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B42" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전현황 공유 COP (ADR-068 · To-Be 전용 효과). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 sdf</x:t>
+          <x:t xml:space="preserve">화면 설정 cop</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="5">
@@ -42994,56 +42994,56 @@
       </x:c>
       <x:c r="C43" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">자위권 발사 (ADR-071·072). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전현황 공유 COP (ADR-068 · To-Be 전용 효과). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 eor</x:t>
+          <x:t xml:space="preserve">화면 설정 sdf</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C44" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">원격 교전 (ADR-070 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">자위권 발사 (ADR-071·072). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 share</x:t>
-        </x:is>
+          <x:t xml:space="preserve">화면 설정 eor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">연합 항적 공유 반사실 (datalink|kvmf-relay|voice|chat|"" , ADR-085). 적용 타입=string, 선언 기본값="". 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">원격 교전 (ADR-070 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 suit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B46" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">화면 설정 share</x:t>
+        </x:is>
       </x:c>
       <x:c r="C46" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">고도대역 적합도 To-Be 복원 (ADR-086 · 반사실). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">연합 항적 공유 반사실 (datalink|kvmf-relay|voice|chat|"" , ADR-085). 적용 타입=string, 선언 기본값="". 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 uavsd</x:t>
+          <x:t xml:space="preserve">화면 설정 suit</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="5">
@@ -43051,14 +43051,14 @@
       </x:c>
       <x:c r="C47" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">무인기 국지방공 자체 교전 (ADR-087 · 반사실). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">고도대역 적합도 To-Be 복원 (ADR-086 · 반사실). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ew</x:t>
+          <x:t xml:space="preserve">화면 설정 uavsd</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="5">
@@ -43066,29 +43066,29 @@
       </x:c>
       <x:c r="C48" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">조기경보 보고원 — 그린파인 보고가 책임 C2에 함께 접수 (ADR-090 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">무인기 국지방공 자체 교전 (ADR-087 · 반사실). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 bsrc</x:t>
+          <x:t xml:space="preserve">화면 설정 ew</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="5">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C49" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 위협 시작 보고원을 조기경보 레이더(그린파인)로 고정 — MCRC 경유 탄도 항적 0건 (ADR-103 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">조기경보 보고원 — 그린파인 보고가 책임 C2에 함께 접수 (ADR-090 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 cue</x:t>
+          <x:t xml:space="preserve">화면 설정 bsrc</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="5">
@@ -43096,44 +43096,44 @@
       </x:c>
       <x:c r="C50" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">사전대기 큐 + 긴급발사 — KAMDOC/IAOC 인지 시 상층 포대에 큐, 큐 받은 포대는 정식 명령 전 발사 가능 (ADR-104 · bsrc=1 전제 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">탄도 위협 시작 보고원을 조기경보 레이더(그린파인)로 고정 — MCRC 경유 탄도 항적 0건 (ADR-103 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 cuegain</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B51">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">화면 설정 cue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C51" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">큐 획득 이득 0~0.95 — 큐 도착 포대 MFR의 탐지→추적→사통 전이 시간을 (1−gain)배 (ADR-104 B-3 · 명시된 근사 · 기본 0). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">사전대기 큐 + 긴급발사 — KAMDOC/IAOC 인지 시 상층 포대에 큐, 큐 받은 포대는 정식 명령 전 발사 가능 (ADR-104 · bsrc=1 전제 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 coal</x:t>
+          <x:t xml:space="preserve">화면 설정 cuegain</x:t>
         </x:is>
       </x:c>
       <x:c r="B52">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C52" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">한미 교전 협조(음성) — THAAD·Patriot C2 ↔ KAMDOC·MCRC/IAOC가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">큐 획득 이득 0~0.95 — 큐 도착 포대 MFR의 탐지→추적→사통 전이 시간을 (1−gain)배 (ADR-104 B-3 · 명시된 근사 · 기본 0). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 rr</x:t>
+          <x:t xml:space="preserve">화면 설정 coal</x:t>
         </x:is>
       </x:c>
       <x:c r="B53">
@@ -43141,14 +43141,14 @@
       </x:c>
       <x:c r="C53" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">책임 C2 보고 재시도 — 상관 실패로 시작 보고가 빈 C2를 5초마다 다시 라우팅 (ADR-106 · THAAD C2 인지 지연 해소 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">한미 교전 협조(음성) — THAAD·Patriot C2 ↔ KAMDOC·MCRC/IAOC가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 nocm</x:t>
+          <x:t xml:space="preserve">화면 설정 rr</x:t>
         </x:is>
       </x:c>
       <x:c r="B54">
@@ -43156,14 +43156,14 @@
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호 순항미사일 교전 제외(양 모드) · 천마는 킬웹에서만 허용 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">책임 C2 보고 재시도 — 상관 실패로 시작 보고가 빈 C2를 5초마다 다시 라우팅 (ADR-106 · THAAD C2 인지 지연 해소 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 shpk</x:t>
+          <x:t xml:space="preserve">화면 설정 nocm</x:t>
         </x:is>
       </x:c>
       <x:c r="B55">
@@ -43171,14 +43171,14 @@
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률 0.7 고정 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호 순항미사일 교전 제외(양 모드) · 천마는 킬웹에서만 허용 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ea</x:t>
+          <x:t xml:space="preserve">화면 설정 shpk</x:t>
         </x:is>
       </x:c>
       <x:c r="B56">
@@ -43186,209 +43186,209 @@
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">조기 사수 지정 — 예상 요격 창 기준으로 항적 접수 시점에 사수를 정하고 「준비되면 쏘라」 명령 (ADR-109 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률 0.7 고정 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B57" s="5">
+          <x:t xml:space="preserve">화면 설정 ea</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C57" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">조기 사수 지정 — 예상 요격 창 기준으로 항적 접수 시점에 사수를 정하고 「준비되면 쏘라」 명령 (ADR-109 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C58" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A59" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
-      <x:c r="B58" s="5">
+      <x:c r="B59" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C58" s="3" t="inlineStr">
+      <x:c r="C59" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="59" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A59" s="2" t="inlineStr">
+    <x:row r="60" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A60" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 pipe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B59" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C59" s="3" t="inlineStr">
+      <x:c r="B60" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C60" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A60" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B60" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B61">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C61" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C62" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 ecs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B62" s="5">
+      <x:c r="B63" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
+      <x:c r="C63" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="63" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A63" s="2" t="inlineStr">
+    <x:row r="64" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A64" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 ecssec</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63">
+      <x:c r="B64">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A64" s="2" t="inlineStr">
+    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A65" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B64" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
+      <x:c r="B65" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C65" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="65" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A65" s="3" t="inlineStr">
+    <x:row r="66" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A66" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B65" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
+      <x:c r="B66" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A67" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B67">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C67" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A68" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C68" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A69" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A70" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B69" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="5">
@@ -43403,7 +43403,7 @@
     <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="5">
@@ -43418,67 +43418,67 @@
     <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C72" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A73" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B72" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C72" s="3" t="inlineStr">
+      <x:c r="B73" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A73" s="3" t="inlineStr">
+    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A74" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B73" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
+      <x:c r="B74" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A74" s="3" t="inlineStr">
+    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A75" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B74" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
+      <x:c r="B75" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A75" s="3" t="inlineStr">
+    <x:row r="76" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A76" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B75" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="5">
@@ -43493,54 +43493,54 @@
     <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B78" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B79" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C79" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A80" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B79" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="5">
@@ -43555,7 +43555,7 @@
     <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43570,7 +43570,7 @@
     <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="5">
@@ -43578,14 +43578,14 @@
       </x:c>
       <x:c r="C82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="5">
@@ -43600,7 +43600,7 @@
     <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43615,7 +43615,7 @@
     <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43630,7 +43630,7 @@
     <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="5">
@@ -43645,7 +43645,7 @@
     <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43660,39 +43660,39 @@
     <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C88" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A89" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
         </x:is>
       </x:c>
-      <x:c r="B88" s="5" t="inlineStr">
+      <x:c r="B89" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">미지정</x:t>
         </x:is>
       </x:c>
-      <x:c r="C88" s="3" t="inlineStr">
+      <x:c r="C89" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A89" s="3" t="inlineStr">
+    <x:row r="90" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A90" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B89" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C89" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A90" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="5">
@@ -43704,10 +43704,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="91" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="5">
@@ -43719,25 +43719,25 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="92" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B92" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C92" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A93" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B92" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C92" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A93" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="7">
@@ -43745,14 +43745,14 @@
       </x:c>
       <x:c r="C93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="7">
@@ -43764,10 +43764,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="7">
@@ -43775,14 +43775,14 @@
       </x:c>
       <x:c r="C95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="7">
@@ -43794,32 +43794,30 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="97" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B97" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A98" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="3" t="inlineStr">
@@ -43831,29 +43829,29 @@
     <x:row r="99" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A99" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B99" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C99" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A100" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B99" s="3" t="inlineStr">
+      <x:c r="B100" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9efb329af4fe162c540a7311015d91afe502cb3c0ddbf77427e1af1ad156ba45</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="3" t="inlineStr">
@@ -43865,12 +43863,12 @@
     <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="3" t="inlineStr">
@@ -43882,29 +43880,29 @@
     <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A102" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B102" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C102" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A103" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B102" s="3" t="inlineStr">
+      <x:c r="B103" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A103" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B103" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6973de42ffd4e594469ebc152bea8be25f65fc6381d86e963a97fc028ac52ff2</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
@@ -43916,12 +43914,12 @@
     <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
+          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
+          <x:t xml:space="preserve">389c53885be546b0a3cbefa0b77fb636b829d1e0ff98b36bb0b06bb87670c910</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="3" t="inlineStr">
@@ -43933,12 +43931,12 @@
     <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">9023d821b4d8d38094983a9b3962900835a2ac0f7bacc0c019dff8d3a8d1041a</x:t>
+          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="3" t="inlineStr">
@@ -43950,15 +43948,32 @@
     <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A106" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1b9656970d24c6290e58a5a0f78e57bc807d1072ae577c9baedcf9e0cfed7187</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A107" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B106" s="3" t="inlineStr">
+      <x:c r="B107" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
-      <x:c r="C106" s="3" t="inlineStr">
+      <x:c r="C107" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 166352715a5a에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 579c2f5ee5ad+dirty에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -16250,25 +16250,20 @@
       </x:c>
       <x:c r="G107" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">음성 협조</x:t>
+          <x:t xml:space="preserve">데이터링크</x:t>
         </x:is>
       </x:c>
       <x:c r="H107">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I107" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">normal(20,σ5)</x:t>
-        </x:is>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L107" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C</x:t>
+          <x:t xml:space="preserve">B</x:t>
         </x:is>
       </x:c>
       <x:c r="M107" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2-VOICE-COORD-01</x:t>
+          <x:t xml:space="preserve">IADS-LINK-SHORT-01</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16295,25 +16290,20 @@
       </x:c>
       <x:c r="G108" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">음성 협조</x:t>
+          <x:t xml:space="preserve">데이터링크</x:t>
         </x:is>
       </x:c>
       <x:c r="H108">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I108" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">normal(20,σ5)</x:t>
-        </x:is>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L108" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C</x:t>
+          <x:t xml:space="preserve">B</x:t>
         </x:is>
       </x:c>
       <x:c r="M108" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2-VOICE-COORD-01</x:t>
+          <x:t xml:space="preserve">IADS-LINK-SHORT-01</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22200,25 +22190,20 @@
       </x:c>
       <x:c r="G251" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">음성 협조</x:t>
+          <x:t xml:space="preserve">데이터링크</x:t>
         </x:is>
       </x:c>
       <x:c r="H251">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I251" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">normal(20,σ5)</x:t>
-        </x:is>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L251" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C</x:t>
+          <x:t xml:space="preserve">B</x:t>
         </x:is>
       </x:c>
       <x:c r="M251" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2-VOICE-COORD-01</x:t>
+          <x:t xml:space="preserve">IADS-LINK-SHORT-01</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22550,25 +22535,20 @@
       </x:c>
       <x:c r="G259" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">음성 협조</x:t>
+          <x:t xml:space="preserve">데이터링크</x:t>
         </x:is>
       </x:c>
       <x:c r="H259">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I259" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">normal(20,σ5)</x:t>
-        </x:is>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L259" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C</x:t>
+          <x:t xml:space="preserve">B</x:t>
         </x:is>
       </x:c>
       <x:c r="M259" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2-VOICE-COORD-01</x:t>
+          <x:t xml:space="preserve">IADS-LINK-SHORT-01</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -42558,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">166352715a5a</x:t>
+          <x:t xml:space="preserve">579c2f5ee5ad+dirty</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43141,7 +43121,7 @@
       </x:c>
       <x:c r="C53" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">한미 교전 협조(음성) — THAAD·Patriot C2 ↔ KAMDOC·MCRC/IAOC가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">한미 교전 협조 — THAAD·Patriot C2 ↔ KAMDOC·MCRC(As-Is 음성)/IAOC(To-Be 데이터링크)가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -43685,7 +43665,7 @@
       </x:c>
       <x:c r="C89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="voice". 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -43851,7 +43831,7 @@
       </x:c>
       <x:c r="B100" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">9efb329af4fe162c540a7311015d91afe502cb3c0ddbf77427e1af1ad156ba45</x:t>
+          <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="3" t="inlineStr">
@@ -43919,7 +43899,7 @@
       </x:c>
       <x:c r="B104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">389c53885be546b0a3cbefa0b77fb636b829d1e0ff98b36bb0b06bb87670c910</x:t>
+          <x:t xml:space="preserve">55657eac6c8954842905b649fd55358844701fc6c4e2f0fbd92d3788e82ebc3b</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="3" t="inlineStr">
@@ -43953,7 +43933,7 @@
       </x:c>
       <x:c r="B106" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1b9656970d24c6290e58a5a0f78e57bc807d1072ae577c9baedcf9e0cfed7187</x:t>
+          <x:t xml:space="preserve">f9e17511001041691028c0d918cce5838e29b224ddfbcd757b264bdbc148dce9</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="3" t="inlineStr">

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 579c2f5ee5ad+dirty에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 806faa842bc8에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42538,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">579c2f5ee5ad+dirty</x:t>
+          <x:t xml:space="preserve">806faa842bc8</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 806faa842bc8에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 edc6addcd3b6에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42538,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">806faa842bc8</x:t>
+          <x:t xml:space="preserve">edc6addcd3b6</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43188,202 +43188,202 @@
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B58" s="5">
+          <x:t xml:space="preserve">화면 설정 cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">사수 지정 되먹임 — 예측을 실제 발사 평가와 같은 조건으로 계산하고, 지정 사수가 예측 준비 시각 + 30초 안에 못 쏘면 「수행 불가」 회신 후 1초 뒤 재지정 (ADR-110 · ea=1일 때만 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C59" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A60" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
-      <x:c r="B59" s="5">
+      <x:c r="B60" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C59" s="3" t="inlineStr">
+      <x:c r="C60" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="60" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A60" s="2" t="inlineStr">
+    <x:row r="61" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A61" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 pipe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B60" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C60" s="3" t="inlineStr">
+      <x:c r="B61" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A61" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B61" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B62">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C62" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C63" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A64" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 ecs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63" s="5">
+      <x:c r="B64" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="64" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A64" s="2" t="inlineStr">
+    <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A65" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 ecssec</x:t>
         </x:is>
       </x:c>
-      <x:c r="B64">
+      <x:c r="B65">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
+      <x:c r="C65" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A65" s="2" t="inlineStr">
+    <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A66" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B65" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
+      <x:c r="B66" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="66" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A66" s="3" t="inlineStr">
+    <x:row r="67" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A67" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B66" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
+      <x:c r="B67" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B67" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A68" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C68" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A69" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B69" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C69" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A71" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B70" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="5">
@@ -43398,7 +43398,7 @@
     <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="5">
@@ -43413,67 +43413,67 @@
     <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A74" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B73" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
+      <x:c r="B74" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A74" s="3" t="inlineStr">
+    <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A75" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B74" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
+      <x:c r="B75" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A75" s="3" t="inlineStr">
+    <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A76" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B75" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C75" s="3" t="inlineStr">
+      <x:c r="B76" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C76" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="76" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A76" s="3" t="inlineStr">
+    <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A77" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B76" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="5">
@@ -43488,54 +43488,54 @@
     <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B79" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B79" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C80" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A81" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B80" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43550,7 +43550,7 @@
     <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="5">
@@ -43565,7 +43565,7 @@
     <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="5">
@@ -43573,14 +43573,14 @@
       </x:c>
       <x:c r="C83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43595,7 +43595,7 @@
     <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43610,7 +43610,7 @@
     <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="5">
@@ -43625,7 +43625,7 @@
     <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43640,7 +43640,7 @@
     <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="5">
@@ -43655,24 +43655,22 @@
     <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B89" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="5">
@@ -43687,22 +43685,24 @@
     <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B91" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="5">
@@ -43717,25 +43717,25 @@
     <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B93" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B93" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B94" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B94" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C94" s="3" t="inlineStr">
@@ -43744,10 +43744,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="7">
@@ -43755,14 +43755,14 @@
       </x:c>
       <x:c r="C95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="7">
@@ -43770,14 +43770,14 @@
       </x:c>
       <x:c r="C96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="7">
@@ -43785,87 +43785,83 @@
       </x:c>
       <x:c r="C97" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A98" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B98" s="7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C98" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A99" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B99" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C99" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A100" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C100" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C101" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A102" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B100" s="3" t="inlineStr">
+      <x:c r="B102" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="3" t="inlineStr">
@@ -43877,46 +43873,46 @@
     <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A103" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B103" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C103" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A105" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B103" s="3" t="inlineStr">
+      <x:c r="B105" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C103" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">55657eac6c8954842905b649fd55358844701fc6c4e2f0fbd92d3788e82ebc3b</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A105" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B105" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="3" t="inlineStr">
@@ -43928,12 +43924,12 @@
     <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A106" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">f9e17511001041691028c0d918cce5838e29b224ddfbcd757b264bdbc148dce9</x:t>
+          <x:t xml:space="preserve">a74c83b703be39cda834cd9a87bb032e6f62dd6904127ce0216c17a757e1b071</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="3" t="inlineStr">
@@ -43945,15 +43941,49 @@
     <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A107" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c09974a1a533cfd2fa82784d91cde9358cd49aa7c738a900535b6f187a412afc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A109" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B107" s="3" t="inlineStr">
+      <x:c r="B109" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
-      <x:c r="C107" s="3" t="inlineStr">
+      <x:c r="C109" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-01 현재 소스 edc6addcd3b6에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-02 현재 소스 4caafb7e5df6+dirty에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42498,7 +42498,7 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="4">
-        <x:v>46296</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="C13" s="3" t="inlineStr">
         <x:is>
@@ -42538,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">edc6addcd3b6</x:t>
+          <x:t xml:space="preserve">4caafb7e5df6+dirty</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43188,7 +43188,7 @@
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 cf</x:t>
+          <x:t xml:space="preserve">화면 설정 bsr</x:t>
         </x:is>
       </x:c>
       <x:c r="B58">
@@ -43196,44 +43196,44 @@
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">사수 지정 되먹임 — 예측을 실제 발사 평가와 같은 조건으로 계산하고, 지정 사수가 예측 준비 시각 + 30초 안에 못 쏘면 「수행 불가」 회신 후 1초 뒤 재지정 (ADR-110 · ea=1일 때만 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">포대 상태 보고 — 결심 C2의 후보 평가가 포대의 마지막 보고 상태(잔탄·채널·레이더 등급)를 씀. 보고 주기 bsrp초 + C2→ECS 계선 대표 지연(카탈로그) 만큼 과거 상태 (ADR-112 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B59" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 bsrp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C59" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">포대 상태 보고 주기(초 · bsr=1일 때). 데이터링크 자동 갱신 개념값 4초 (IADS-STATUS-RPT-01). 적용 타입=number, 선언 기본값=4. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B60" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">화면 설정 cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C60" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="52.79999923706055" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">사수 지정 되먹임 — 예측을 실제 발사 평가와 같은 조건으로 계산하고, 지정 사수가 예측 준비 시각 + 30초 안에 못 쏘면 「수행 불가」 회신 후 1초 뒤 재지정 (ADR-110 · ea=1일 때만 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 pipe</x:t>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="5">
@@ -43241,59 +43241,59 @@
       </x:c>
       <x:c r="C61" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
+          <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="5">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C62" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B63">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 pipe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C63" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ecs</x:t>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C64" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ecssec</x:t>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
         </x:is>
       </x:c>
       <x:c r="B65">
@@ -43301,119 +43301,119 @@
       </x:c>
       <x:c r="C65" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 ecs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">화면 설정 ecssec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A68" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B66" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
+      <x:c r="B68" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C68" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="67" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A67" s="3" t="inlineStr">
+    <x:row r="69" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A69" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B67" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
+      <x:c r="B69" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B68" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B69">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A70" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="5">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C70" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C71" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A72" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C72" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A73" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B71" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B72" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="5">
@@ -43428,7 +43428,7 @@
     <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A74" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="5">
@@ -43440,10 +43440,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A75" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="5">
@@ -43458,7 +43458,7 @@
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
+          <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="5">
@@ -43473,7 +43473,7 @@
     <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
+          <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="5">
@@ -43488,7 +43488,7 @@
     <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="5">
@@ -43500,42 +43500,40 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C79" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A80" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C80" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43547,25 +43545,27 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="82" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B82" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="5">
@@ -43580,7 +43580,7 @@
     <x:row r="84" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43588,14 +43588,14 @@
       </x:c>
       <x:c r="C84" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43603,14 +43603,14 @@
       </x:c>
       <x:c r="C85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="5">
@@ -43625,7 +43625,7 @@
     <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43640,7 +43640,7 @@
     <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="5">
@@ -43655,7 +43655,7 @@
     <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 batteryStatusReporting</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="5">
@@ -43670,39 +43670,37 @@
     <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 statusReportPeriodSec</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="5">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=4. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B91" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="5">
@@ -43717,7 +43715,7 @@
     <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="5">
@@ -43729,10 +43727,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="94" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="5">
@@ -43747,25 +43745,27 @@
     <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B95" s="7">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B95" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B96" s="7">
+          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B96" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C96" s="3" t="inlineStr">
@@ -43774,13 +43774,13 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="97" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B97" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C97" s="3" t="inlineStr">
@@ -43789,25 +43789,25 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A98" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B98" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B98" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C98" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A99" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="7">
@@ -43822,97 +43822,89 @@
     <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A100" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C100" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B101" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A102" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B102" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C102" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B103" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B103" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C104" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="104" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="3" t="inlineStr">
@@ -43924,66 +43916,134 @@
     <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A106" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A110" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">a74c83b703be39cda834cd9a87bb032e6f62dd6904127ce0216c17a757e1b071</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C106" s="3" t="inlineStr">
+      <x:c r="B110" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">e7229bef90c709daed3ab789b7ca10780e136574fc6f899ca2f227a58d293ec1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C110" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A107" s="3" t="inlineStr">
+    <x:row r="111" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A111" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B107" s="3" t="inlineStr">
+      <x:c r="B111" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
-      <x:c r="C107" s="3" t="inlineStr">
+      <x:c r="C111" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="108" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A108" s="3" t="inlineStr">
+    <x:row r="112" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A112" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
         </x:is>
       </x:c>
-      <x:c r="B108" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c09974a1a533cfd2fa82784d91cde9358cd49aa7c738a900535b6f187a412afc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C108" s="3" t="inlineStr">
+      <x:c r="B112" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ae9ad7cdf5892cefcbb7f1d4935d79868abaf6ffbfa890fc99894417002fedda</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C112" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="109" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A109" s="3" t="inlineStr">
+    <x:row r="113" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A113" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B109" s="3" t="inlineStr">
+      <x:c r="B113" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
-      <x:c r="C109" s="3" t="inlineStr">
+      <x:c r="C113" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-02 현재 소스 4caafb7e5df6+dirty에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-03 현재 소스 80877dbc9493에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42498,7 +42498,7 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="4">
-        <x:v>46297</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="C13" s="3" t="inlineStr">
         <x:is>
@@ -42538,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4caafb7e5df6+dirty</x:t>
+          <x:t xml:space="preserve">80877dbc9493</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43091,44 +43091,44 @@
       </x:c>
       <x:c r="C51" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">사전대기 큐 + 긴급발사 — KAMDOC/IAOC 인지 시 상층 포대에 큐, 큐 받은 포대는 정식 명령 전 발사 가능 (ADR-104 · bsrc=1 전제 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">사전대기 큐 — KAMDOC/IAOC 인지 시 요격 창이 있는 상층 포대 전부에 표적 정보·준비 지시 (ADR-104 · bsrc=1 전제 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 발사 권한은 cuefire가 정함. 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 cuegain</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B52">
+          <x:t xml:space="preserve">화면 설정 cuefire</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C52" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">큐 획득 이득 0~0.95 — 큐 도착 포대 MFR의 탐지→추적→사통 전이 시간을 (1−gain)배 (ADR-104 B-3 · 명시된 근사 · 기본 0). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">큐에 발사 권한 포함 — 1이면 큐를 받은 포대가 자기 조건이 갖춰지면 정식 명령 없이 쏨(긴급발사 ② · 종전 기본). 0이면 표준 절차: 큐는 준비만, 발사는 지휘소의 사수 지정 명령으로, 포대 자체 발사는 자위권 ③(낙하점 10km 이내·자기 레이더·마감 직전)만 (ADR-113). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 coal</x:t>
+          <x:t xml:space="preserve">화면 설정 cuegain</x:t>
         </x:is>
       </x:c>
       <x:c r="B53">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C53" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">한미 교전 협조 — THAAD·Patriot C2 ↔ KAMDOC·MCRC(As-Is 음성)/IAOC(To-Be 데이터링크)가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">큐 획득 이득 0~0.95 — 큐 도착 포대 MFR의 탐지→추적→사통 전이 시간을 (1−gain)배 (ADR-104 B-3 · 명시된 근사 · 기본 0). 적용 타입=number, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 rr</x:t>
+          <x:t xml:space="preserve">화면 설정 coal</x:t>
         </x:is>
       </x:c>
       <x:c r="B54">
@@ -43136,14 +43136,14 @@
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">책임 C2 보고 재시도 — 상관 실패로 시작 보고가 빈 C2를 5초마다 다시 라우팅 (ADR-106 · THAAD C2 인지 지연 해소 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">한미 교전 협조 — THAAD·Patriot C2 ↔ KAMDOC·MCRC(As-Is 음성)/IAOC(To-Be 데이터링크)가 최적 사수를 협조해 정함, 마감 임박·시한 초과면 협조 없이 발사 (ADR-105 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 nocm</x:t>
+          <x:t xml:space="preserve">화면 설정 rr</x:t>
         </x:is>
       </x:c>
       <x:c r="B55">
@@ -43151,14 +43151,14 @@
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호 순항미사일 교전 제외(양 모드) · 천마는 킬웹에서만 허용 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">책임 C2 보고 재시도 — 상관 실패로 시작 보고가 빈 C2를 5초마다 다시 라우팅 (ADR-106 · THAAD C2 인지 지연 해소 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 shpk</x:t>
+          <x:t xml:space="preserve">화면 설정 nocm</x:t>
         </x:is>
       </x:c>
       <x:c r="B56">
@@ -43166,14 +43166,14 @@
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률 0.7 고정 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호 순항미사일 교전 제외(양 모드) · 천마는 킬웹에서만 허용 (ADR-107 ① · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 ea</x:t>
+          <x:t xml:space="preserve">화면 설정 shpk</x:t>
         </x:is>
       </x:c>
       <x:c r="B57">
@@ -43181,14 +43181,14 @@
       </x:c>
       <x:c r="C57" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">조기 사수 지정 — 예상 요격 창 기준으로 항적 접수 시점에 사수를 정하고 「준비되면 쏘라」 명령 (ADR-109 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">비호·천마 소형 무인기·순항 요격확률 0.7 고정 (ADR-107 ② · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 bsr</x:t>
+          <x:t xml:space="preserve">화면 설정 ea</x:t>
         </x:is>
       </x:c>
       <x:c r="B58">
@@ -43196,239 +43196,239 @@
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">포대 상태 보고 — 결심 C2의 후보 평가가 포대의 마지막 보고 상태(잔탄·채널·레이더 등급)를 씀. 보고 주기 bsrp초 + C2→ECS 계선 대표 지연(카탈로그) 만큼 과거 상태 (ADR-112 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">조기 사수 지정 — 예상 요격 창 기준으로 항적 접수 시점에 사수를 정하고 「준비되면 쏘라」 명령 (ADR-109 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 bsrp</x:t>
+          <x:t xml:space="preserve">화면 설정 bsr</x:t>
         </x:is>
       </x:c>
       <x:c r="B59">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C59" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">포대 상태 보고 주기(초 · bsr=1일 때). 데이터링크 자동 갱신 개념값 4초 (IADS-STATUS-RPT-01). 적용 타입=number, 선언 기본값=4. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">포대 상태 보고 — 결심 C2의 후보 평가가 포대의 마지막 보고 상태(잔탄·채널·레이더 등급)를 씀. 보고 주기 bsrp초 + C2→ECS 계선 대표 지연(카탈로그) 만큼 과거 상태 (ADR-112 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 cf</x:t>
+          <x:t xml:space="preserve">화면 설정 bsrp</x:t>
         </x:is>
       </x:c>
       <x:c r="B60">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C60" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">사수 지정 되먹임 — 예측을 실제 발사 평가와 같은 조건으로 계산하고, 지정 사수가 예측 준비 시각 + 30초 안에 못 쏘면 「수행 불가」 회신 후 1초 뒤 재지정 (ADR-110 · ea=1일 때만 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">포대 상태 보고 주기(초 · bsr=1일 때). 데이터링크 자동 갱신 개념값 4초 (IADS-STATUS-RPT-01). 적용 타입=number, 선언 기본값=4. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 lx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B61" s="5">
+          <x:t xml:space="preserve">화면 설정 cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C61" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">사수 지정 되먹임 — 예측을 실제 발사 평가와 같은 조건으로 계산하고, 지정 사수가 예측 준비 시각 + 30초 안에 못 쏘면 「수행 불가」 회신 후 1초 뒤 재지정 (ADR-110 · ea=1일 때만 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 lx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C62" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">탄도 축선 발사점 연장 — 대표 사거리부터 비행, 탐지 선착이 기하에서 나옴 (ADR-091 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
-      <x:c r="B62" s="5">
+      <x:c r="B63" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
+      <x:c r="C63" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="63" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A63" s="2" t="inlineStr">
+    <x:row r="64" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A64" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 pipe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
+      <x:c r="B64" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A64" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B64" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B65">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C65" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A67" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 ecs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B66" s="5">
+      <x:c r="B67" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
+      <x:c r="C67" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A67" s="2" t="inlineStr">
+    <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A68" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 ecssec</x:t>
         </x:is>
       </x:c>
-      <x:c r="B67">
+      <x:c r="B68">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
+      <x:c r="C68" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A68" s="2" t="inlineStr">
+    <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A69" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B68" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
+      <x:c r="B69" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="69" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A69" s="3" t="inlineStr">
+    <x:row r="70" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A70" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B69" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
+      <x:c r="B70" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B70" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A71" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B71">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C71" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B72" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A74" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B73" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="5">
@@ -43443,7 +43443,7 @@
     <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A75" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="5">
@@ -43458,67 +43458,67 @@
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B76" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C76" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A77" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B76" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C76" s="3" t="inlineStr">
+      <x:c r="B77" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C77" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A77" s="3" t="inlineStr">
+    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A78" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B77" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C77" s="3" t="inlineStr">
+      <x:c r="B78" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C78" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A78" s="3" t="inlineStr">
+    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A79" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B78" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C78" s="3" t="inlineStr">
+      <x:c r="B79" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C79" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A79" s="3" t="inlineStr">
+    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A80" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B79" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="5">
@@ -43533,54 +43533,54 @@
     <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C81" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B82" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B83" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C83" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A84" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B83" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C83" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A84" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="5">
@@ -43595,7 +43595,7 @@
     <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A85" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43610,7 +43610,7 @@
     <x:row r="86" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="5">
@@ -43618,14 +43618,14 @@
       </x:c>
       <x:c r="C86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43637,25 +43637,27 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="88" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B88" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 standbyCueAuthority</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">fire</x:t>
+        </x:is>
       </x:c>
       <x:c r="C88" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="prepare". 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A89" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 batteryStatusReporting</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="5">
@@ -43670,22 +43672,22 @@
     <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 statusReportPeriodSec</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="5">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=4. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
+          <x:t xml:space="preserve">엔진 기본 batteryStatusReporting</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="5">
@@ -43700,22 +43702,22 @@
     <x:row r="92" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 statusReportPeriodSec</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="5">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=4. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="5">
@@ -43730,7 +43732,7 @@
     <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="5">
@@ -43745,24 +43747,22 @@
     <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B95" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B95" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="39.599998474121094" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="5">
@@ -43777,22 +43777,24 @@
     <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B97" s="5">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
       </x:c>
       <x:c r="C97" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A98" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="5">
@@ -43807,25 +43809,25 @@
     <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A99" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B99" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B99" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C99" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A100" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B100" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C100" s="3" t="inlineStr">
@@ -43834,10 +43836,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="7">
@@ -43845,14 +43847,14 @@
       </x:c>
       <x:c r="C101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A102" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="7">
@@ -43860,14 +43862,14 @@
       </x:c>
       <x:c r="C102" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="7">
@@ -43875,87 +43877,83 @@
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A104" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B104" s="7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C104" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="105" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B105" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B105" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A106" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C107" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A108" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B106" s="3" t="inlineStr">
+      <x:c r="B108" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A107" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B107" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C107" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A108" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B108" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="3" t="inlineStr">
@@ -43967,46 +43965,46 @@
     <x:row r="109" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A109" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A110" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B110" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C110" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A111" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B109" s="3" t="inlineStr">
+      <x:c r="B111" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C109" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">e7229bef90c709daed3ab789b7ca10780e136574fc6f899ca2f227a58d293ec1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A111" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B111" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" s="3" t="inlineStr">
@@ -44018,12 +44016,12 @@
     <x:row r="112" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A112" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ae9ad7cdf5892cefcbb7f1d4935d79868abaf6ffbfa890fc99894417002fedda</x:t>
+          <x:t xml:space="preserve">72cb369a9108877b7fea288175ca0dfd31fd4bbb5e5cbaa42c187e4c06964b56</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" s="3" t="inlineStr">
@@ -44035,15 +44033,49 @@
     <x:row r="113" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A113" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B113" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C113" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A114" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B114" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ed027a7f2f9fe171b9802787cd83b46e923f8159fabedf23bd9da7a47b16266d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C114" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A115" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B113" s="3" t="inlineStr">
+      <x:c r="B115" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
         </x:is>
       </x:c>
-      <x:c r="C113" s="3" t="inlineStr">
+      <x:c r="C115" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>

--- a/K-JAMDS_파라미터.xlsx
+++ b/K-JAMDS_파라미터.xlsx
@@ -311,7 +311,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>K-JAMDS 파라미터 참조본. 2026-10-03 현재 소스 80877dbc9493에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
+        <x:v>K-JAMDS 파라미터 참조본. 2026-10-04 현재 소스 71fa288c2f51+dirty에서 재내보냈습니다. 고친 셀은 scripts/import-params-xlsx.mjs로 가져와 엔진에 덮어쓸 수 있습니다(ADR-108).</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -42498,7 +42498,7 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="4">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="C13" s="3" t="inlineStr">
         <x:is>
@@ -42538,7 +42538,7 @@
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">80877dbc9493</x:t>
+          <x:t xml:space="preserve">71fa288c2f51+dirty</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="inlineStr">
@@ -43263,187 +43263,187 @@
     <x:row r="63" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 alx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">공중 위협 발사점 연장 — 순항·전투기·무인기도 발사·이륙 원점(위협 제원 launchStandoffKm)부터 비행, 생성 기준을 탄도와 같게 (ADR-114 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A64" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 floor</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63" s="5">
+      <x:c r="B64" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
+      <x:c r="C64" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 처리 시간 바닥 — 체계 처리 구간 + 운용자 판단을 따로 추첨, 평균 불변 (ADR-092 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="64" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A64" s="2" t="inlineStr">
+    <x:row r="65" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A65" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 pipe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B64" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
+      <x:c r="B65" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C65" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">협조 파이프라인 현실화 — 실행가능 사수 있을 때만 협조 요청 · 회신은 협조 계선 역방향 · C2A 회신 처리 큐 (ADR-093 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A65" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 icc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B65" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B66">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 icc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="5">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C66" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">ICC 중계 인가 — 교전명령을 ICC가 접수·인가하고 권역 내 재배정/반송 (ADR-094 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">화면 설정 iccsec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICC 중계 인가 시간(초) 민감도 — 미지정(-1)이면 ICC 기본 9초, 0이면 재검증 로직만 (ADR-094). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A68" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">화면 설정 ecs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B67" s="5">
+      <x:c r="B68" s="5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
+      <x:c r="C68" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간 ADSIM 정합 — 교전명령 실행을 10초로 (ADR-095 · 양 모드 공통 · 기본 꺼짐). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A68" s="2" t="inlineStr">
+    <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A69" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 ecssec</x:t>
         </x:is>
       </x:c>
-      <x:c r="B68">
+      <x:c r="B69">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
+      <x:c r="C69" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ECS 실행 시간(초) 민감도 — 미지정(-1)이면 10초 (ADR-095). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A69" s="2" t="inlineStr">
+    <x:row r="70" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A70" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 aim</x:t>
         </x:is>
       </x:c>
-      <x:c r="B69" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
+      <x:c r="B70" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">표적 카탈로그 — 탄도탄이 조준점 10점을 나눠 노린다 (ADR-097 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="70" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A70" s="3" t="inlineStr">
+    <x:row r="71" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A71" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">화면 설정 par</x:t>
         </x:is>
       </x:c>
-      <x:c r="B70" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C70" s="3" t="inlineStr">
+      <x:c r="B71" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C71" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C2 결심 시간 동일화 — To-Be 결심 노드(IAOC) 운용자 판단 시간을 As-Is 결심 노드(KAMDOC·MCRC)와 같게 (ADR-099 · codex 정합 · 이 화면만 기본 켜짐, 엔진 기본은 꺼짐). 적용 타입=boolean, 선언 기본값=1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">화면 설정 issue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B71" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B72">
-        <x:v>-1</x:v>
+          <x:t xml:space="preserve">화면 설정 issue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C72" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
+          <x:t xml:space="preserve">교전명령 발령 작업 — 결심 노드가 명령을 낼 때마다 큐를 탄다 (ADR-096 · 기본 꺼짐: ADSIM에는 없는 비용). 적용 타입=boolean, 선언 기본값=0. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A73" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B73" s="5">
-        <x:v>1</x:v>
+          <x:t xml:space="preserve">화면 설정 issuesec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="C73" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">발령 시간(초) 민감도 — 미지정(-1)이면 노드 체계 성분(KAMDOC 7.5·IAOC 1.5초) (ADR-096). 적용 타입=number, 선언 기본값=-1. 출처: prototype/command-flow.html PARAMS/파서</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A74" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 highResolutionDeployment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A75" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 threatTargetDispersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B74" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="5">
@@ -43458,7 +43458,7 @@
     <x:row r="76" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A76" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+          <x:t xml:space="preserve">엔진 기본 southernAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="5">
@@ -43473,67 +43473,67 @@
     <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 linkSemanticsV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C77" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A78" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 sensorReportParity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B77" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C77" s="3" t="inlineStr">
+      <x:c r="B78" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C78" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A78" s="3" t="inlineStr">
+    <x:row r="79" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A79" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 sawtoothFreshness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B78" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C78" s="3" t="inlineStr">
+      <x:c r="B79" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C79" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A79" s="3" t="inlineStr">
+    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A80" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 approvalChain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B79" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C79" s="3" t="inlineStr">
+      <x:c r="B80" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C80" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A80" s="3" t="inlineStr">
+    <x:row r="81" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A81" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 unifiedEngagementState</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B80" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="5">
@@ -43548,54 +43548,54 @@
     <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+          <x:t xml:space="preserve">엔진 기본 selfDefenseFire</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C82" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B83" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">미지정</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 engageOnRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B83" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C83" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A84" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 usfkTrackSharing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B84" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미지정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C84" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=null. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A85" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 wtaSuitability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B84" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C84" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A85" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="5">
@@ -43610,7 +43610,7 @@
     <x:row r="86" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A86" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
+          <x:t xml:space="preserve">엔진 기본 uavLocalSelfEngage</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="5">
@@ -43625,7 +43625,7 @@
     <x:row r="87" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyWarningReport</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="5">
@@ -43633,46 +43633,46 @@
       </x:c>
       <x:c r="C87" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="88" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A88" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 ballisticReportSource</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C88" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A89" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 standbyCueAuthority</x:t>
         </x:is>
       </x:c>
-      <x:c r="B88" s="5" t="inlineStr">
+      <x:c r="B89" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">fire</x:t>
         </x:is>
       </x:c>
-      <x:c r="C88" s="3" t="inlineStr">
+      <x:c r="C89" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값="prepare". 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A89" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B89" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C89" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
+          <x:t xml:space="preserve">엔진 기본 standbyCue</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="5">
@@ -43687,7 +43687,7 @@
     <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A91" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 batteryStatusReporting</x:t>
+          <x:t xml:space="preserve">엔진 기본 earlyShooterAssignment</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="5">
@@ -43702,37 +43702,37 @@
     <x:row r="92" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 statusReportPeriodSec</x:t>
+          <x:t xml:space="preserve">엔진 기본 batteryStatusReporting</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="5">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C92" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=4. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
+          <x:t xml:space="preserve">엔진 기본 statusReportPeriodSec</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="5">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C93" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=4. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A94" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
+          <x:t xml:space="preserve">엔진 기본 assignmentFeedback</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="5">
@@ -43747,7 +43747,7 @@
     <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A95" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradCruiseExclusion</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="5">
@@ -43762,7 +43762,7 @@
     <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A96" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+          <x:t xml:space="preserve">엔진 기본 shoradPkRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="5">
@@ -43777,39 +43777,39 @@
     <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A97" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">엔진 기본 commanderRouteRetry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B97" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C97" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A98" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">엔진 기본 rokUsfkCoordination</x:t>
         </x:is>
       </x:c>
-      <x:c r="B97" s="5" t="inlineStr">
+      <x:c r="B98" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">미지정</x:t>
         </x:is>
       </x:c>
-      <x:c r="C97" s="3" t="inlineStr">
+      <x:c r="C98" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값={"asis":"voice","tobe":"datalink"}. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A98" s="3" t="inlineStr">
+    <x:row r="99" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A99" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">엔진 기본 ballisticLaunchAxes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B98" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="5">
@@ -43824,7 +43824,7 @@
     <x:row r="100" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A100" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+          <x:t xml:space="preserve">엔진 기본 airLaunchAxes</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="5">
@@ -43839,25 +43839,25 @@
     <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B101" s="7">
+          <x:t xml:space="preserve">엔진 기본 threatAimpoints</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B101" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C101" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A102" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B102" s="7">
+          <x:t xml:space="preserve">엔진 기본 c2DecisionTimeParity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B102" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C102" s="3" t="inlineStr">
@@ -43866,10 +43866,10 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="103" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
+          <x:t xml:space="preserve">엔진 기본 c2ServiceFloor</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="7">
@@ -43877,14 +43877,14 @@
       </x:c>
       <x:c r="C103" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="104" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 approvalPipelineRealism</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="7">
@@ -43892,14 +43892,14 @@
       </x:c>
       <x:c r="C104" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="26.399999618530273" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A105" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+          <x:t xml:space="preserve">엔진 기본 iccRelayAuthorization</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="7">
@@ -43907,87 +43907,83 @@
       </x:c>
       <x:c r="C105" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=true. 출처: js/engine/sim-engine.js</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A106" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 기본 ecsExecutionTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B106" s="7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C106" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="106" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="107" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A107" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B107" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
-        </x:is>
+          <x:t xml:space="preserve">엔진 기본 directiveIssueTime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" s="7">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C107" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+          <x:t xml:space="preserve">features를 명시하지 않은 Simulation 생성값. 화면 전달값=false. 출처: js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="108" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A108" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/system-types.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c9b3efd9d9ed4de363745ede9b35eac3045ef1b1c0273ec489dd3c9074cbb262</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C108" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/config/deployments.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bb4ca552f32432da3a5b8374e7d0a7585f138c3e639f8b8ab5d6aa92831f89cf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C109" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A110" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/config/deployment-adapter.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B108" s="3" t="inlineStr">
+      <x:c r="B110" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9f9c20ceed0551f2cb259e969f4c4c40e328b85843b3bfd9baff322bd38d3682</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C108" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A109" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B109" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">155bd9ec551fd24488dffd8fbe2af0fec6e86b09b4b43641aa4e5d2e779d6047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C109" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c05ca5f35b544b42d770adae4dc85fedaea526e00268bcb916915be6536eda8d</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" s="3" t="inlineStr">
@@ -43999,46 +43995,46 @@
     <x:row r="111" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A111" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/threats.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B111" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6bb541f7294d4bb9f82cc7f1098e45002c30fc07cf76881138a849a0b669d5be</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C111" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A112" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 js/data/axes.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B112" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">631347fd11a907604fab56ca7731df5ba8d532c984ea384d6efaa271de3a6337</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C112" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A113" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 js/data/scenarios.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="B111" s="3" t="inlineStr">
+      <x:c r="B113" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">e0d14eb11a8488ca646dbede9700c794eea4b878d6b9bf65ab6807745230c92f</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C111" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A112" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B112" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">72cb369a9108877b7fea288175ca0dfd31fd4bbb5e5cbaa42c187e4c06964b56</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C112" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A113" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B113" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" s="3" t="inlineStr">
@@ -44050,12 +44046,12 @@
     <x:row r="114" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A114" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+          <x:t xml:space="preserve">SHA-256 js/engine/sim-engine.js</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ed027a7f2f9fe171b9802787cd83b46e923f8159fabedf23bd9da7a47b16266d</x:t>
+          <x:t xml:space="preserve">607f3eea5d04d1123b57823e200685f97d9aed3dd2390b92061e663446d05b8b</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" s="3" t="inlineStr">
@@ -44067,15 +44063,49 @@
     <x:row r="115" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A115" s="3" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SHA-256 js/model/iads/c2-agent.js</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B115" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">d697f803fbf208fcaa952c26ab81720d227b00a6c7592d1025b6cffcb12b5d6f</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C115" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A116" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SHA-256 prototype/command-flow.html</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B116" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">29ddfa9a3a0aca1e35acc6f0282305134730445ba26c29fc2f7d0a3d28f3d467</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C116" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A117" s="3" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">SHA-256 scripts/export-params-xlsx.mjs</x:t>
         </x:is>
       </x:c>
-      <x:c r="B115" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dfb5b486ea4210e5ebf0026e8b83ac72056322f7b2f6c0f3c7d81c172f50b170</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C115" s="3" t="inlineStr">
+      <x:c r="B117" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1596aa2e1e353db4fb8df777ada9d8c7bc895a550790bf90b069160b9fbbd7bc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C117" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">작업 파일 내용 해시. 경로는 저장소 루트 기준</x:t>
         </x:is>
@@ -70804,55 +70834,60 @@
       </x:c>
       <x:c r="I1" s="1" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">발사·이륙 이격거리 km(ADR-114)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="1" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">발사권역</x:t>
         </x:is>
       </x:c>
-      <x:c r="J1" s="1" t="inlineStr">
+      <x:c r="K1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">단가M$</x:t>
         </x:is>
       </x:c>
-      <x:c r="K1" s="1" t="inlineStr">
+      <x:c r="L1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">교전권 보유 C2 As-Is</x:t>
         </x:is>
       </x:c>
-      <x:c r="L1" s="1" t="inlineStr">
+      <x:c r="M1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">교전권 보유 C2 To-Be</x:t>
         </x:is>
       </x:c>
-      <x:c r="M1" s="1" t="inlineStr">
+      <x:c r="N1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">자동화 As-Is</x:t>
         </x:is>
       </x:c>
-      <x:c r="N1" s="1" t="inlineStr">
+      <x:c r="O1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">자동화 To-Be</x:t>
         </x:is>
       </x:c>
-      <x:c r="O1" s="1" t="inlineStr">
+      <x:c r="P1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">조준점 대상</x:t>
         </x:is>
       </x:c>
-      <x:c r="P1" s="1" t="inlineStr">
+      <x:c r="Q1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">출처(paramRef)</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q1" s="1" t="inlineStr">
+      <x:c r="R1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">사거리출처</x:t>
         </x:is>
       </x:c>
-      <x:c r="R1" s="1" t="inlineStr">
+      <x:c r="S1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">단가출처</x:t>
         </x:is>
       </x:c>
-      <x:c r="S1" s="1" t="inlineStr">
+      <x:c r="T1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">비고</x:t>
         </x:is>
@@ -70889,50 +70924,53 @@
       <x:c r="H2">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="I2" t="inlineStr">
+      <x:c r="I2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dmz, coastal</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2">
+      <x:c r="K2">
         <x:v>0.01</x:v>
       </x:c>
-      <x:c r="K2" t="inlineStr">
+      <x:c r="L2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M2" t="inlineStr">
+      <x:c r="N2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" t="inlineStr">
+      <x:c r="O2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">auto-preauth</x:t>
         </x:is>
       </x:c>
-      <x:c r="O2" t="inlineStr">
+      <x:c r="P2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="P2" t="inlineStr">
+      <x:c r="Q2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-UAV-RCS-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q2" t="inlineStr">
+      <x:c r="R2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-UAV-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R2" t="inlineStr">
+      <x:c r="S2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-UAV-COST-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="S2" t="inlineStr">
+      <x:c r="T2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2022.12.26 침투 사건 모사. 저탐지·항적소실 반복. To-Be는 사전승인 자동교전(위협별 자동화 차등).</x:t>
         </x:is>
@@ -70969,50 +71007,53 @@
       <x:c r="H3">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="I3" t="inlineStr">
+      <x:c r="I3">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dmz, coastal</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3">
+      <x:c r="K3">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="K3" t="inlineStr">
+      <x:c r="L3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="L3" t="inlineStr">
+      <x:c r="M3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">IAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M3" t="inlineStr">
+      <x:c r="N3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N3" t="inlineStr">
+      <x:c r="O3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-on-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="O3" t="inlineStr">
+      <x:c r="P3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="P3" t="inlineStr">
+      <x:c r="Q3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-AN2-RCS-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q3" t="inlineStr">
+      <x:c r="R3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-AN2-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R3" t="inlineStr">
+      <x:c r="S3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-AN2-COST-01</x:t>
         </x:is>
@@ -71049,50 +71090,53 @@
       <x:c r="H4">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="I4" t="inlineStr">
+      <x:c r="I4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dmz, coastal</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4">
+      <x:c r="K4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K4" t="inlineStr">
+      <x:c r="L4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="L4" t="inlineStr">
+      <x:c r="M4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">IAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M4" t="inlineStr">
+      <x:c r="N4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N4" t="inlineStr">
+      <x:c r="O4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-on-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="O4" t="inlineStr">
+      <x:c r="P4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="P4" t="inlineStr">
+      <x:c r="Q4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-HELI-RCS-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q4" t="inlineStr">
+      <x:c r="R4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-HELI-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R4" t="inlineStr">
+      <x:c r="S4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-HELI-COST-01</x:t>
         </x:is>
@@ -71129,50 +71173,53 @@
       <x:c r="H5">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="I5" t="inlineStr">
+      <x:c r="I5">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dmz, coastal, deep</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5">
+      <x:c r="K5">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K5" t="inlineStr">
+      <x:c r="L5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="L5" t="inlineStr">
+      <x:c r="M5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">IAOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" t="inlineStr">
+      <x:c r="N5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N5" t="inlineStr">
+      <x:c r="O5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-on-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="O5" t="inlineStr">
+      <x:c r="P5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="P5" t="inlineStr">
+      <x:c r="Q5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SEN-ACR-PD-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q5" t="inlineStr">
+      <x:c r="R5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-FTR-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R5" t="inlineStr">
+      <x:c r="S5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-FTR-COST-01</x:t>
         </x:is>
@@ -71209,50 +71256,53 @@
       <x:c r="H6">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="I6" t="inlineStr">
+      <x:c r="I6">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dmz, coastal, deep</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6">
+      <x:c r="K6">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="K6" t="inlineStr">
+      <x:c r="L6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MCRC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" t="inlineStr">
+      <x:c r="N6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N6" t="inlineStr">
+      <x:c r="O6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-on-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="O6" t="inlineStr">
+      <x:c r="P6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="P6" t="inlineStr">
+      <x:c r="Q6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-CM-RCS-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q6" t="inlineStr">
+      <x:c r="R6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-CM-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R6" t="inlineStr">
+      <x:c r="S6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-CM-COST-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="S6" t="inlineStr">
+      <x:c r="T6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">To-Be: Human-on-the-loop 자동교전 대상.</x:t>
         </x:is>
@@ -71289,50 +71339,50 @@
       <x:c r="H7">
         <x:v>690</x:v>
       </x:c>
-      <x:c r="I7" t="inlineStr">
+      <x:c r="J7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">deep</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7">
+      <x:c r="K7">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" t="inlineStr">
+      <x:c r="L7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAMDOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" t="inlineStr">
+      <x:c r="N7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N7" t="inlineStr">
+      <x:c r="O7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">auto-preauth</x:t>
         </x:is>
       </x:c>
-      <x:c r="O7" t="inlineStr">
+      <x:c r="P7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Y</x:t>
         </x:is>
       </x:c>
-      <x:c r="P7" t="inlineStr">
+      <x:c r="Q7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SEN-GPR-PD-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q7" t="inlineStr">
+      <x:c r="R7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-KN23-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R7" t="inlineStr">
+      <x:c r="S7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-KN23-COST-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="S7" t="inlineStr">
+      <x:c r="T7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">비행시간 수분 이내 — 승인 지연이 곧 요격기회 상실. To-Be 사전승인 자동교전. 종심 발사→광역 표적(저각 발사 시 단축 가능, rangeBandKm.min은 정합검증 미사용).</x:t>
         </x:is>
@@ -71369,50 +71419,50 @@
       <x:c r="H8">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="I8" t="inlineStr">
+      <x:c r="J8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">deep</x:t>
         </x:is>
       </x:c>
-      <x:c r="J8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K8" t="inlineStr">
+      <x:c r="K8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">KAMDOC</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" t="inlineStr">
+      <x:c r="N8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">human-in-loop</x:t>
         </x:is>
       </x:c>
-      <x:c r="N8" t="inlineStr">
+      <x:c r="O8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">auto-preauth</x:t>
         </x:is>
       </x:c>
-      <x:c r="O8" t="inlineStr">
+      <x:c r="P8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Y</x:t>
         </x:is>
       </x:c>
-      <x:c r="P8" t="inlineStr">
+      <x:c r="Q8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-KN25-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q8" t="inlineStr">
+      <x:c r="R8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-KN25-RNG-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="R8" t="inlineStr">
+      <x:c r="S8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">THR-KN25-COST-01</x:t>
         </x:is>
       </x:c>
-      <x:c r="S8" t="inlineStr">
+      <x:c r="T8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">발사간격 약 20초 연발 — 포화 유발 위협. 중거리 종심 발사권역.</x:t>
         </x:is>
